--- a/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
+++ b/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K340"/>
+  <dimension ref="A1:K341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Tabulados Básicos</t>
+          <t>Por Tipo</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -6854,17 +6854,17 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>TRABAJO-2001-2023.xls</t>
+          <t>POR-TIPO-1998-2025.xlsx</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/TRABAJO-2001-2023.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/POR-TIPO-1998-2025.xlsx</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Por Tipo</t>
+          <t>Por Variable</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>POR-TIPO-1998-2023.xlsx</t>
+          <t>POR-VARIABLE-1998-2025.xlsx</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-TIPO-1998-2023.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/POR-VARIABLE-1998-2025.xlsx</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Por Variable</t>
+          <t>Divorcios</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Encuesta de hogares</t>
+          <t>Estadísticas vitales</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>POR-VARIABLE-1998-2023.xlsx</t>
+          <t>DIVORCIOS.xls</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-VARIABLE-1998-2023.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/DIVORCIOS.xls</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Divorcios</t>
+          <t>Por Entidad</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>DIVORCIOS.xls</t>
+          <t>POR-ENTIDAD-Defunciones.xls</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/DIVORCIOS.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Defunciones.xls</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>POR-ENTIDAD-Defunciones.xls</t>
+          <t>POR-ENTIDAD-Matrimonios.xls</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Defunciones.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Matrimonios.xls</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>POR-ENTIDAD-Matrimonios.xls</t>
+          <t>POR-ENTIDAD-nacimientos.xls</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Matrimonios.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-nacimientos.xls</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Por Entidad</t>
+          <t>Por Municipios</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>POR-ENTIDAD-nacimientos.xls</t>
+          <t>POR-MUNICIPIOS-DEFUNCIONES.xls</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-nacimientos.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-DEFUNCIONES.xls</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>POR-MUNICIPIOS-DEFUNCIONES.xls</t>
+          <t>POR-MUNICIPIOS-Matrimonios.xls</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-DEFUNCIONES.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-Matrimonios.xls</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>POR-MUNICIPIOS-Matrimonios.xls</t>
+          <t>POR-MUNICIPIOS-nacimientos.xls</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-Matrimonios.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-nacimientos.xls</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Por Municipios</t>
+          <t>Suicidios</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>POR-MUNICIPIOS-nacimientos.xls</t>
+          <t>SUICIDIOS.xls</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-nacimientos.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/SUICIDIOS.xls</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Suicidios</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas vitales</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>SUICIDIOS.xls</t>
+          <t>Amazonas.xls</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/SUICIDIOS.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Amazonas.xls</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>Amazonas.xls</t>
+          <t>Estado-Amazonas-1.xls</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Amazonas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-1.xls</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>Estado-Amazonas-1.xls</t>
+          <t>Estado-Amazonas.xls</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas.xls</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>Estado-Amazonas.xls</t>
+          <t>Estado_Amazonas-3.xls</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Amazonas-3.xls</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Estado_Amazonas-3.xls</t>
+          <t>Anzoategui.xls</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Amazonas-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Anzoategui.xls</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>Anzoategui.xls</t>
+          <t>Estado-Anzoategui-1.xls</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Anzoategui.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-1.xls</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>Estado-Anzoategui-1.xls</t>
+          <t>Estado-Anzoategui.xls</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui.xls</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>Estado-Anzoategui.xls</t>
+          <t>Estado_Anzoategui-3.xls</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Anzoategui-3.xls</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>Estado_Anzoategui-3.xls</t>
+          <t>Apure.xls</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Anzoategui-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Apure.xls</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>Apure.xls</t>
+          <t>Estado-Apure-1.xls</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Apure.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-1.xls</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>Estado-Apure-1.xls</t>
+          <t>Estado-Apure.xls</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure.xls</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>Estado-Apure.xls</t>
+          <t>Estado_Apure-3.xls</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Apure-3.xls</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>Estado_Apure-3.xls</t>
+          <t>Barinas.xls</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Apure-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Barinas.xls</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>Barinas.xls</t>
+          <t>Estado-Barinas-1.xls</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Barinas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas-1.xls</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>Estado-Barinas-1.xls</t>
+          <t>Estado-Barinas.xls</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas.xls</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>Estado-Barinas.xls</t>
+          <t>Estado_Barinas-3.xls</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Barinas-3.xls</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>Estado_Barinas-3.xls</t>
+          <t>Bolivar.xls</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Barinas-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Bolivar.xls</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>Bolivar.xls</t>
+          <t>Estado-Bolivar-1.xls</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Bolivar.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-1.xls</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>Estado-Bolivar-1.xls</t>
+          <t>Estado-Bolivar.xls</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar.xls</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>Estado-Bolivar.xls</t>
+          <t>Estado_Bolivar-4.xls</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Bolivar-4.xls</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>Estado_Bolivar-4.xls</t>
+          <t>Carabobo.xls</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Bolivar-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Carabobo.xls</t>
         </is>
       </c>
       <c r="K146" s="4" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>Carabobo.xls</t>
+          <t>Estado-Carabobo-1.xls</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Carabobo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-1.xls</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>Estado-Carabobo-1.xls</t>
+          <t>Estado-Carabobo.xls</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo.xls</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>Estado-Carabobo.xls</t>
+          <t>Estado_Carabobo-4.xls</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Carabobo-4.xls</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>Estado_Carabobo-4.xls</t>
+          <t>Cojedes.xls</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Carabobo-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Cojedes.xls</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>Cojedes.xls</t>
+          <t>Estado-Cojedes-1.xls</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Cojedes.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-1.xls</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes-1.xls</t>
+          <t>Estado-Cojedes.xls</t>
         </is>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes.xls</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes.xls</t>
+          <t>Estado_Cojedes-5.xls</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Cojedes-5.xls</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>Estado_Cojedes-5.xls</t>
+          <t>Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Cojedes-5.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>Delta-Amacuro.xls</t>
+          <t>Estado-Delta-Amacuro-1.xls</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Delta-Amacuro.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-1.xls</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>Estado-Delta-Amacuro-1.xls</t>
+          <t>Estado-Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>Estado-Delta-Amacuro.xls</t>
+          <t>Estado_DeltaAmacuro-4.xls</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_DeltaAmacuro-4.xls</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Dep. Federales</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Estado_DeltaAmacuro-4.xls</t>
+          <t>Dependencias-Federales-1.xls</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_DeltaAmacuro-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-1.xls</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>Dependencias-Federales-1.xls</t>
+          <t>Dependencias-Federales.xls</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales.xls</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Dep. Federales</t>
+          <t>Dependencias Federales</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -9367,12 +9367,12 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Dependencias-Federales.xls</t>
+          <t>Dependencias_Federales-3.xls</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias_Federales-3.xls</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Dependencias Federales</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>Dependencias_Federales-3.xls</t>
+          <t>Distrito-Capital-1.xls</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias_Federales-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-1.xls</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Distrito-Capital-1.xls</t>
+          <t>Distrito-Capital-2.xls</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-2.xls</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>Distrito-Capital-2.xls</t>
+          <t>Distrito-Capital.xls</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-2.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital.xls</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>Distrito-Capital.xls</t>
+          <t>Distrito_Capital-3.xls</t>
         </is>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito_Capital-3.xls</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>Distrito_Capital-3.xls</t>
+          <t>Estado-Falcon-1.xls</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito_Capital-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-1.xls</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>Estado-Falcon-1.xls</t>
+          <t>Estado-Falcon.xls</t>
         </is>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon.xls</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>Estado-Falcon.xls</t>
+          <t>Estado_Falcon-4.xls</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Falcon-4.xls</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Estado_Falcon-4.xls</t>
+          <t>Falcon.xls</t>
         </is>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Falcon-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Falcon.xls</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>Falcon.xls</t>
+          <t>Estado-Guarico-1.xls</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Falcon.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-1.xls</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico-1.xls</t>
+          <t>Estado-Guarico.xls</t>
         </is>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico.xls</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico.xls</t>
+          <t>Estado_Guarico-4.xls</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Guarico-4.xls</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>Estado_Guarico-4.xls</t>
+          <t>Guarico.xls</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Guarico-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Guarico.xls</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Guarico.xls</t>
+          <t>Estado-La-Guaira-1.xls</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Guarico.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-1.xls</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira-1.xls</t>
+          <t>Estado-La-Guaira.xls</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira.xls</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira.xls</t>
+          <t>Estado_Vargas-4.xls</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Vargas-4.xls</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>Estado_Vargas-4.xls</t>
+          <t>Vargas.xls</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Vargas-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Vargas.xls</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>Vargas.xls</t>
+          <t>Estado-Lara-1.xls</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Vargas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-1.xls</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>Estado-Lara-1.xls</t>
+          <t>Estado-Lara.xls</t>
         </is>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara.xls</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>Estado-Lara.xls</t>
+          <t>Estado_Lara-3.xls</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Lara-3.xls</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>Estado_Lara-3.xls</t>
+          <t>Lara.xls</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Lara-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lara.xls</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>Lara.xls</t>
+          <t>Estado-Miranda-1.xls</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lara.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-1.xls</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>Estado-Miranda-1.xls</t>
+          <t>Estado-Miranda.xls</t>
         </is>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda.xls</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>Estado-Miranda.xls</t>
+          <t>Estado_Miranda-5.xls</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Miranda-5.xls</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
@@ -10735,12 +10735,12 @@
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>Estado_Miranda-5.xls</t>
+          <t>Miranda.xls</t>
         </is>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Miranda-5.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Miranda.xls</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>Miranda.xls</t>
+          <t>Estado-Monagas-1.xls</t>
         </is>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Miranda.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-1.xls</t>
         </is>
       </c>
       <c r="K185" s="4" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>Estado-Monagas-1.xls</t>
+          <t>Estado-Monagas.xls</t>
         </is>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas.xls</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>Estado-Monagas.xls</t>
+          <t>Estado_Monagas-4.xls</t>
         </is>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Monagas-4.xls</t>
         </is>
       </c>
       <c r="K187" s="4" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>Estado_Monagas-4.xls</t>
+          <t>Monagas.xls</t>
         </is>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Monagas-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Monagas.xls</t>
         </is>
       </c>
       <c r="K188" s="4" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>Monagas.xls</t>
+          <t>Estado-Merida-1.xls</t>
         </is>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Monagas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-1.xls</t>
         </is>
       </c>
       <c r="K189" s="4" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>Estado-Merida-1.xls</t>
+          <t>Estado-Merida.xls</t>
         </is>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida.xls</t>
         </is>
       </c>
       <c r="K190" s="4" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>Estado-Merida.xls</t>
+          <t>Estado_Merida-4.xls</t>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Merida-4.xls</t>
         </is>
       </c>
       <c r="K191" s="4" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>Estado_Merida-4.xls</t>
+          <t>Merida.xls</t>
         </is>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Merida-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Merida.xls</t>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>Merida.xls</t>
+          <t>Nacional-1.xls</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Merida.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-1.xls</t>
         </is>
       </c>
       <c r="K193" s="4" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>Nacional-1.xls</t>
+          <t>Nacional.xls</t>
         </is>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional.xls</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>Nacional.xls</t>
+          <t>Estado-Nueva-Esparta-1.xls</t>
         </is>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta-1.xls</t>
         </is>
       </c>
       <c r="K195" s="4" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t>Estado-Nueva-Esparta-1.xls</t>
+          <t>Estado-Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="K196" s="4" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>Estado-Nueva-Esparta.xls</t>
+          <t>Estado_NuevaEsparta-4.xls</t>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_NuevaEsparta-4.xls</t>
         </is>
       </c>
       <c r="K197" s="4" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
-          <t>Estado_NuevaEsparta-4.xls</t>
+          <t>Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_NuevaEsparta-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="K198" s="4" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="I199" s="4" t="inlineStr">
         <is>
-          <t>Nueva-Esparta.xls</t>
+          <t>Estado-Portuguesa-1.xls</t>
         </is>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nueva-Esparta.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa-1.xls</t>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr">
@@ -11647,12 +11647,12 @@
       </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
-          <t>Estado-Portuguesa-1.xls</t>
+          <t>Estado-Portuguesa.xls</t>
         </is>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa.xls</t>
         </is>
       </c>
       <c r="K200" s="4" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="I201" s="4" t="inlineStr">
         <is>
-          <t>Estado-Portuguesa.xls</t>
+          <t>Estado_Portuguesa-4.xls</t>
         </is>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Portuguesa-4.xls</t>
         </is>
       </c>
       <c r="K201" s="4" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
-          <t>Estado_Portuguesa-4.xls</t>
+          <t>Portuguesa.xls</t>
         </is>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Portuguesa-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Portuguesa.xls</t>
         </is>
       </c>
       <c r="K202" s="4" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="I203" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa.xls</t>
+          <t>Estado-Sucre-1.xls</t>
         </is>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Portuguesa.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-1.xls</t>
         </is>
       </c>
       <c r="K203" s="4" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
-          <t>Estado-Sucre-1.xls</t>
+          <t>Estado-Sucre.xls</t>
         </is>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre.xls</t>
         </is>
       </c>
       <c r="K204" s="4" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="I205" s="4" t="inlineStr">
         <is>
-          <t>Estado-Sucre.xls</t>
+          <t>Estado_Sucre-6.xls</t>
         </is>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Sucre-6.xls</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="I206" s="4" t="inlineStr">
         <is>
-          <t>Estado_Sucre-6.xls</t>
+          <t>Sucre.xls</t>
         </is>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Sucre-6.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Sucre.xls</t>
         </is>
       </c>
       <c r="K206" s="4" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Tachira</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="I207" s="4" t="inlineStr">
         <is>
-          <t>Sucre.xls</t>
+          <t>Estado-Tachira.xls</t>
         </is>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Sucre.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira.xls</t>
         </is>
       </c>
       <c r="K207" s="4" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Tachira</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -12103,12 +12103,12 @@
       </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
-          <t>Estado-Tachira.xls</t>
+          <t>Estado-Trujillo-1.xls</t>
         </is>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-1.xls</t>
         </is>
       </c>
       <c r="K208" s="4" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="I209" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo-1.xls</t>
+          <t>Estado-Trujillo.xls</t>
         </is>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo.xls</t>
         </is>
       </c>
       <c r="K209" s="4" t="inlineStr">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.xls</t>
+          <t>Estado_Trujillo-3.xls</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Trujillo-3.xls</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="I211" s="4" t="inlineStr">
         <is>
-          <t>Estado_Trujillo-3.xls</t>
+          <t>Trujillo.xls</t>
         </is>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Trujillo-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Trujillo.xls</t>
         </is>
       </c>
       <c r="K211" s="4" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
-          <t>Trujillo.xls</t>
+          <t>Estado-Tachira-1.xls</t>
         </is>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Trujillo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-1.xls</t>
         </is>
       </c>
       <c r="K212" s="4" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="I213" s="4" t="inlineStr">
         <is>
-          <t>Estado-Tachira-1.xls</t>
+          <t>Estado_Tachira-8.xls</t>
         </is>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Tachira-8.xls</t>
         </is>
       </c>
       <c r="K213" s="4" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="I214" s="4" t="inlineStr">
         <is>
-          <t>Estado_Tachira-8.xls</t>
+          <t>Tachira.xls</t>
         </is>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Tachira-8.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tachira.xls</t>
         </is>
       </c>
       <c r="K214" s="4" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>Tachira.xls</t>
+          <t>Estado-Yaracuy-1.xls</t>
         </is>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tachira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy-1.xls</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr">
@@ -12559,12 +12559,12 @@
       </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy-1.xls</t>
+          <t>Estado-Yaracuy.xls</t>
         </is>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy.xls</t>
         </is>
       </c>
       <c r="K216" s="4" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy.xls</t>
+          <t>Estado_Yaracuy-4.xls</t>
         </is>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Yaracuy-4.xls</t>
         </is>
       </c>
       <c r="K217" s="4" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="I218" s="4" t="inlineStr">
         <is>
-          <t>Estado_Yaracuy-4.xls</t>
+          <t>Yaracuy.xls</t>
         </is>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Yaracuy-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Yaracuy.xls</t>
         </is>
       </c>
       <c r="K218" s="4" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy.xls</t>
+          <t>Estado-Zulia-1.xls</t>
         </is>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Yaracuy.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-1.xls</t>
         </is>
       </c>
       <c r="K219" s="4" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="I220" s="4" t="inlineStr">
         <is>
-          <t>Estado-Zulia-1.xls</t>
+          <t>Estado-Zulia.xls</t>
         </is>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia.xls</t>
         </is>
       </c>
       <c r="K220" s="4" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="I221" s="4" t="inlineStr">
         <is>
-          <t>Estado-Zulia.xls</t>
+          <t>Estado_Zulia-6.xls</t>
         </is>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Zulia-6.xls</t>
         </is>
       </c>
       <c r="K221" s="4" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
-          <t>Estado_Zulia-6.xls</t>
+          <t>Zulia.xls</t>
         </is>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Zulia-6.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Zulia.xls</t>
         </is>
       </c>
       <c r="K222" s="4" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Coeficiente GINI</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -12953,17 +12953,17 @@
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t>Zulia.xls</t>
+          <t>Coeficiente-GINI-2025-1.xlsx</t>
         </is>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Zulia.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Coeficiente-GINI-2025-1.xlsx</t>
         </is>
       </c>
       <c r="K223" s="4" t="inlineStr">
@@ -12985,27 +12985,27 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Estructura Poblacional</t>
+          <t>Tabulados Básicos</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Población</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -13015,12 +13015,12 @@
       </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
-          <t>Estructura-completa.pdf</t>
+          <t>TRABAJO-1999-2025-1.xlsx</t>
         </is>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/09/Estructura-completa.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/TRABAJO-1999-2025-1.xlsx</t>
         </is>
       </c>
       <c r="K224" s="4" t="inlineStr">
@@ -13042,12 +13042,12 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Población 1950-2050</t>
+          <t>Estructura Poblacional</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Población</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -13062,22 +13062,22 @@
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I225" s="4" t="inlineStr">
         <is>
-          <t>1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
+          <t>Estructura-completa.pdf</t>
         </is>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/09/Estructura-completa.pdf</t>
         </is>
       </c>
       <c r="K225" s="4" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Edad Simple</t>
+          <t>Población 1950-2050</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -13109,12 +13109,12 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -13124,17 +13124,17 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
-          <t>EDAD-SIMPLE.xls</t>
+          <t>1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
         </is>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
         </is>
       </c>
       <c r="K226" s="4" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Esperanza de Vida</t>
+          <t>Edad Simple</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t>ESPERANZA-DE-VIDA.xls</t>
+          <t>EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="K227" s="4" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Esperanza de Vida</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
-          <t>Nacional-36.xls</t>
+          <t>ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="K228" s="4" t="inlineStr">
@@ -13270,42 +13270,42 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>7T FILVEN</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
+          <t>Nacional-36.xls</t>
         </is>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
         </is>
       </c>
       <c r="K229" s="4" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>7T FILVEN</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -13347,22 +13347,22 @@
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ABRIL_2025.pdf</t>
+          <t>TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
         </is>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ABRIL_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
         </is>
       </c>
       <c r="K230" s="4" t="inlineStr">
@@ -13409,17 +13409,17 @@
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ABRIL_2026.pdf</t>
+          <t>Resumen_ABRIL_2025.pdf</t>
         </is>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/05/Resumen_ABRIL_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ABRIL_2025.pdf</t>
         </is>
       </c>
       <c r="K231" s="4" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>Resumen_AGOSTO_2025.pdf</t>
+          <t>Resumen_ABRIL_2026.pdf</t>
         </is>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_AGOSTO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/05/Resumen_ABRIL_2026.pdf</t>
         </is>
       </c>
       <c r="K232" s="4" t="inlineStr">
@@ -13523,17 +13523,17 @@
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I233" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto-9.pdf</t>
+          <t>Resumen_AGOSTO_2025.pdf</t>
         </is>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-9.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_AGOSTO_2025.pdf</t>
         </is>
       </c>
       <c r="K233" s="4" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -13575,22 +13575,22 @@
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I234" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-AMAZONAS.pdf</t>
+          <t>Noticias-Agosto-9.pdf</t>
         </is>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-AMAZONAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-9.pdf</t>
         </is>
       </c>
       <c r="K234" s="4" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -13642,12 +13642,12 @@
       </c>
       <c r="I235" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ANZOATEGUI.pdf</t>
+          <t>ESTADO-AMAZONAS.pdf</t>
         </is>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ANZOATEGUI.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-AMAZONAS.pdf</t>
         </is>
       </c>
       <c r="K235" s="4" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -13699,12 +13699,12 @@
       </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-APURE.pdf</t>
+          <t>ESTADO-ANZOATEGUI.pdf</t>
         </is>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-APURE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ANZOATEGUI.pdf</t>
         </is>
       </c>
       <c r="K236" s="4" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Aviso Oficial Fe de Vida 2026</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -13746,22 +13746,22 @@
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I237" s="4" t="inlineStr">
         <is>
-          <t>AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
+          <t>ESTADO-APURE.pdf</t>
         </is>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/01/AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-APURE.pdf</t>
         </is>
       </c>
       <c r="K237" s="4" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Aviso Oficial Fe de Vida 2026</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -13803,22 +13803,22 @@
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-BARINAS.pdf</t>
+          <t>AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BARINAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/01/AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="K238" s="4" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="I239" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-BOLIVAR.pdf</t>
+          <t>ESTADO-BARINAS.pdf</t>
         </is>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BOLIVAR.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BARINAS.pdf</t>
         </is>
       </c>
       <c r="K239" s="4" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>CATÁLOGO ACADÉMICO</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -13922,17 +13922,17 @@
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I240" s="4" t="inlineStr">
         <is>
-          <t>CatalogoDic2025-modificado.pdf</t>
+          <t>ESTADO-BOLIVAR.pdf</t>
         </is>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/12/CatalogoDic2025-modificado.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BOLIVAR.pdf</t>
         </is>
       </c>
       <c r="K240" s="4" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>CATÁLOGO ACADÉMICO</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -13974,22 +13974,22 @@
       </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="I241" s="4" t="inlineStr">
         <is>
-          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>CatalogoDic2025-modificado.pdf</t>
         </is>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/12/CatalogoDic2025-modificado.pdf</t>
         </is>
       </c>
       <c r="K241" s="4" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -14031,22 +14031,22 @@
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I242" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-CARABOBO.pdf</t>
+          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-CARABOBO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="K242" s="4" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -14098,12 +14098,12 @@
       </c>
       <c r="I243" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-COJEDES.pdf</t>
+          <t>ESTADO-CARABOBO.pdf</t>
         </is>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-COJEDES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-CARABOBO.pdf</t>
         </is>
       </c>
       <c r="K243" s="4" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Defensa Integral de la Nación e Innovación en la Fuerza Armada Nacional Bolivariana</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -14145,22 +14145,22 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I244" s="4" t="inlineStr">
         <is>
-          <t>ART1DEFENSAINTEGRAL.pdf</t>
+          <t>ESTADO-COJEDES.pdf</t>
         </is>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART1DEFENSAINTEGRAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-COJEDES.pdf</t>
         </is>
       </c>
       <c r="K244" s="4" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Defensa Integral de la Nación e Innovación en la Fuerza Armada Nacional Bolivariana</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -14202,22 +14202,22 @@
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I245" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-DELTA-AMACURO.pdf</t>
+          <t>ART1DEFENSAINTEGRAL.pdf</t>
         </is>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-DELTA-AMACURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART1DEFENSAINTEGRAL.pdf</t>
         </is>
       </c>
       <c r="K245" s="4" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Dependencias Federales</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -14264,17 +14264,17 @@
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I246" s="4" t="inlineStr">
         <is>
-          <t>Folleto-de-las-Dependencias-Federales.pdf</t>
+          <t>ESTADO-DELTA-AMACURO.pdf</t>
         </is>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-de-las-Dependencias-Federales.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-DELTA-AMACURO.pdf</t>
         </is>
       </c>
       <c r="K246" s="4" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Diciembre</t>
+          <t>Dependencias Federales</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -14316,22 +14316,22 @@
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I247" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
+          <t>Folleto-de-las-Dependencias-Federales.pdf</t>
         </is>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-de-las-Dependencias-Federales.pdf</t>
         </is>
       </c>
       <c r="K247" s="4" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Directrices</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -14373,22 +14373,22 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>DIRECTRICES.pdf</t>
+          <t>RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/DIRECTRICES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K248" s="4" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Directrices</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -14430,22 +14430,22 @@
       </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I249" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
+          <t>DIRECTRICES.pdf</t>
         </is>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/DIRECTRICES.pdf</t>
         </is>
       </c>
       <c r="K249" s="4" t="inlineStr">
@@ -14492,17 +14492,17 @@
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr">
         <is>
-          <t>DISTRITO-CAPITAL.pdf</t>
+          <t>Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
         </is>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/DISTRITO-CAPITAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
         </is>
       </c>
       <c r="K250" s="4" t="inlineStr">
@@ -14524,19 +14524,19 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
+          <t>Distrito Capital</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr">
+        <is>
+          <t>Publicaciones</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
           <t>Documento</t>
         </is>
       </c>
-      <c r="D251" s="4" t="inlineStr">
-        <is>
-          <t>Publicaciones</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
@@ -14549,17 +14549,17 @@
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTO-SEGEN.pdf</t>
+          <t>DISTRITO-CAPITAL.pdf</t>
         </is>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/DOCUMENTO-SEGEN.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/DISTRITO-CAPITAL.pdf</t>
         </is>
       </c>
       <c r="K251" s="4" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Documento Técnico EHM</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -14601,22 +14601,22 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I252" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTO-TECNICO-EHM.pdf</t>
+          <t>DOCUMENTO-SEGEN.pdf</t>
         </is>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/DOCUMENTO-TECNICO-EHM.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/DOCUMENTO-SEGEN.pdf</t>
         </is>
       </c>
       <c r="K252" s="4" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>El Estado Docente y sus implicaciones jurídicas-filosóficas</t>
+          <t>Documento Técnico EHM</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -14658,22 +14658,22 @@
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr">
         <is>
-          <t>ART5ESTADODOCENTE.pdf</t>
+          <t>DOCUMENTO-TECNICO-EHM.pdf</t>
         </is>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART5ESTADODOCENTE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/DOCUMENTO-TECNICO-EHM.pdf</t>
         </is>
       </c>
       <c r="K253" s="4" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>El Estado Docente y sus implicaciones jurídicas-filosóficas</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -14720,17 +14720,17 @@
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN_NOTAS_ENERO_2026.pdf</t>
+          <t>ART5ESTADODOCENTE.pdf</t>
         </is>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_ENERO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART5ESTADODOCENTE.pdf</t>
         </is>
       </c>
       <c r="K254" s="4" t="inlineStr">
@@ -14782,12 +14782,12 @@
       </c>
       <c r="I255" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ENERO_2025.pdf</t>
+          <t>RESUMEN_NOTAS_ENERO_2026.pdf</t>
         </is>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ENERO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_ENERO_2026.pdf</t>
         </is>
       </c>
       <c r="K255" s="4" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Estado Amazonas</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -14829,22 +14829,22 @@
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I256" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
+          <t>Resumen_ENERO_2025.pdf</t>
         </is>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ENERO_2025.pdf</t>
         </is>
       </c>
       <c r="K256" s="4" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Estado Anzoátegui</t>
+          <t>Estado Amazonas</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="I257" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K257" s="4" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Estado Apure</t>
+          <t>Estado Anzoátegui</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="I258" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Apure-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Apure-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K258" s="4" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Estado Barinas</t>
+          <t>Estado Apure</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -15010,12 +15010,12 @@
       </c>
       <c r="I259" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
+          <t>Folleto-del-Estado-Apure-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Apure-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K259" s="4" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Estado Bolívar</t>
+          <t>Estado Barinas</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -15067,12 +15067,12 @@
       </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
+          <t>Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
         </is>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
         </is>
       </c>
       <c r="K260" s="4" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Estado Carabobo</t>
+          <t>Estado Bolívar</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -15124,12 +15124,12 @@
       </c>
       <c r="I261" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K261" s="4" t="inlineStr">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Estado Cojedes</t>
+          <t>Estado Carabobo</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -15181,12 +15181,12 @@
       </c>
       <c r="I262" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes.pdf</t>
+          <t>Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Cojedes.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K262" s="4" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Estado Delta Amacuro</t>
+          <t>Estado Cojedes</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -15238,12 +15238,12 @@
       </c>
       <c r="I263" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
+          <t>Estado-Cojedes.pdf</t>
         </is>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Cojedes.pdf</t>
         </is>
       </c>
       <c r="K263" s="4" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Estado Falcón</t>
+          <t>Estado Delta Amacuro</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="I264" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Falcon-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Falcon-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K264" s="4" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Estado Guárico</t>
+          <t>Estado Falcón</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="I265" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico_20250620_153508_0000.pdf</t>
+          <t>Folleto-del-Estado-Falcon-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Guarico_20250620_153508_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Falcon-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K265" s="4" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Estado La Guaira</t>
+          <t>Estado Guárico</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="I266" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira.pdf</t>
+          <t>Estado-Guarico_20250620_153508_0000.pdf</t>
         </is>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-La-Guaira.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Guarico_20250620_153508_0000.pdf</t>
         </is>
       </c>
       <c r="K266" s="4" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Estado Lara</t>
+          <t>Estado La Guaira</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="I267" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Lara-INE-2025.pdf</t>
+          <t>Estado-La-Guaira.pdf</t>
         </is>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Lara-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-La-Guaira.pdf</t>
         </is>
       </c>
       <c r="K267" s="4" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Estado Miranda</t>
+          <t>Estado Lara</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="I268" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Miranda-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Lara-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Miranda-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Lara-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K268" s="4" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Estado Monagas</t>
+          <t>Estado Miranda</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -15580,12 +15580,12 @@
       </c>
       <c r="I269" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Monagas-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Miranda-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Monagas-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Miranda-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K269" s="4" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Estado Mérida</t>
+          <t>Estado Monagas</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -15637,12 +15637,12 @@
       </c>
       <c r="I270" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Merida-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Monagas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Merida-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Monagas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K270" s="4" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Estado Nueva Esparta</t>
+          <t>Estado Mérida</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -15694,12 +15694,12 @@
       </c>
       <c r="I271" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
+          <t>Folleto-del-Estado-Merida-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Merida-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Estado Portuguesa</t>
+          <t>Estado Nueva Esparta</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -15751,12 +15751,12 @@
       </c>
       <c r="I272" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
+          <t>Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
         </is>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
         </is>
       </c>
       <c r="K272" s="4" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Estado Sucre</t>
+          <t>Estado Portuguesa</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="I273" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Sucre-INE-2025.pdf</t>
+          <t>Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
         </is>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Sucre-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
         </is>
       </c>
       <c r="K273" s="4" t="inlineStr">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Estado Trujillo</t>
+          <t>Estado Sucre</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="I274" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Folleto-del-Estado-Sucre-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Sucre-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K274" s="4" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Estado Táchira</t>
+          <t>Estado Trujillo</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -15922,12 +15922,12 @@
       </c>
       <c r="I275" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Estado-Tachira.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Tachira.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K275" s="4" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Estado Yaracuy</t>
+          <t>Estado Táchira</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="I276" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy_20250619_231832_0000.pdf</t>
+          <t>Folleto-Estado-Tachira.pdf</t>
         </is>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Yaracuy_20250619_231832_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Tachira.pdf</t>
         </is>
       </c>
       <c r="K276" s="4" t="inlineStr">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Estado Zulia</t>
+          <t>Estado Yaracuy</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="I277" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Zulia-INE-2025.pdf</t>
+          <t>Estado-Yaracuy_20250619_231832_0000.pdf</t>
         </is>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Zulia-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Yaracuy_20250619_231832_0000.pdf</t>
         </is>
       </c>
       <c r="K277" s="4" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas Basadas en Registros</t>
+          <t>Estado Zulia</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -16083,22 +16083,22 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I278" s="4" t="inlineStr">
         <is>
-          <t>ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
+          <t>Folleto-del-Estado-Zulia-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Zulia-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K278" s="4" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Estudio de la narrativa audiovisual como espacio de autodescubrimiento</t>
+          <t>Estadísticas Basadas en Registros</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -16140,22 +16140,22 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I279" s="4" t="inlineStr">
         <is>
-          <t>ART6CINEYSUBJETIVIDAD.pdf</t>
+          <t>ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART6CINEYSUBJETIVIDAD.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K279" s="4" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Estudio de la narrativa audiovisual como espacio de autodescubrimiento</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -16197,22 +16197,22 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I280" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-FALCON.pdf</t>
+          <t>ART6CINEYSUBJETIVIDAD.pdf</t>
         </is>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-FALCON.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART6CINEYSUBJETIVIDAD.pdf</t>
         </is>
       </c>
       <c r="K280" s="4" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -16254,22 +16254,22 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I281" s="4" t="inlineStr">
         <is>
-          <t>Resumen_FEBRERO_2025.pdf</t>
+          <t>ESTADO-FALCON.pdf</t>
         </is>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_FEBRERO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-FALCON.pdf</t>
         </is>
       </c>
       <c r="K281" s="4" t="inlineStr">
@@ -16316,17 +16316,17 @@
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I282" s="4" t="inlineStr">
         <is>
-          <t>febrero.pdf</t>
+          <t>Resumen_FEBRERO_2025.pdf</t>
         </is>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/febrero.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_FEBRERO_2025.pdf</t>
         </is>
       </c>
       <c r="K282" s="4" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Flyer</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -16368,22 +16368,22 @@
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I283" s="4" t="inlineStr">
         <is>
-          <t>Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
+          <t>febrero.pdf</t>
         </is>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/febrero.pdf</t>
         </is>
       </c>
       <c r="K283" s="4" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Folleto en PDF</t>
+          <t>Flyer</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -16430,17 +16430,17 @@
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I284" s="4" t="inlineStr">
         <is>
-          <t>TRANSICION-DEMOGRAFICA.pdf</t>
+          <t>Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
         </is>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/TRANSICION-DEMOGRAFICA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
         </is>
       </c>
       <c r="K284" s="4" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Formato de Fe de Vida 2026</t>
+          <t>Folleto en PDF</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -16482,22 +16482,22 @@
       </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I285" s="4" t="inlineStr">
         <is>
-          <t>FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
+          <t>TRANSICION-DEMOGRAFICA.pdf</t>
         </is>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/01/FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/TRANSICION-DEMOGRAFICA.pdf</t>
         </is>
       </c>
       <c r="K285" s="4" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Gestion y Mantenimiento</t>
+          <t>Formato de Fe de Vida 2026</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -16539,22 +16539,22 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="I286" s="4" t="inlineStr">
         <is>
-          <t>GESTION-Y-MANTENIMIENTO.pdf</t>
+          <t>FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/GESTION-Y-MANTENIMIENTO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/01/FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="K286" s="4" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Grandes Misiones Habitacionales</t>
+          <t>Gestion y Mantenimiento</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -16596,22 +16596,22 @@
       </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I287" s="4" t="inlineStr">
         <is>
-          <t>Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
+          <t>GESTION-Y-MANTENIMIENTO.pdf</t>
         </is>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/GESTION-Y-MANTENIMIENTO.pdf</t>
         </is>
       </c>
       <c r="K287" s="4" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>Grandes Misiones Habitacionales</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -16653,22 +16653,22 @@
       </c>
       <c r="G288" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-GUARICO.pdf</t>
+          <t>Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
         </is>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-GUARICO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
         </is>
       </c>
       <c r="K288" s="4" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>INE – FILVEN</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -16715,17 +16715,17 @@
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
+          <t>ESTADO-GUARICO.pdf</t>
         </is>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-GUARICO.pdf</t>
         </is>
       </c>
       <c r="K289" s="4" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>INE – FILVEN</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -16767,22 +16767,22 @@
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
-          <t>25-anos-Encuesta-Industrial-.pdf</t>
+          <t>TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
         </is>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/25-anos-Encuesta-Industrial-.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
         </is>
       </c>
       <c r="K290" s="4" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -16829,17 +16829,17 @@
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JULIO_2025.pdf</t>
+          <t>25-anos-Encuesta-Industrial-.pdf</t>
         </is>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JULIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/25-anos-Encuesta-Industrial-.pdf</t>
         </is>
       </c>
       <c r="K291" s="4" t="inlineStr">
@@ -16886,17 +16886,17 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Julio-31.pdf</t>
+          <t>Resumen_JULIO_2025.pdf</t>
         </is>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JULIO_2025.pdf</t>
         </is>
       </c>
       <c r="K292" s="4" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -16943,17 +16943,17 @@
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I293" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JUNIO_2025.pdf</t>
+          <t>Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="K293" s="4" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
-          <t>Noticias-12-06-al-19-06.pdf</t>
+          <t>Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="K294" s="4" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -17052,22 +17052,22 @@
       </c>
       <c r="G295" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LA-GUAIRA.pdf</t>
+          <t>Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="K295" s="4" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -17119,12 +17119,12 @@
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LARA.pdf</t>
+          <t>ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="K296" s="4" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Las escala subregional y local en la planificación</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -17166,22 +17166,22 @@
       </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I297" s="4" t="inlineStr">
         <is>
-          <t>E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="K297" s="4" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Las escala subregional y local en la planificación</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -17223,22 +17223,22 @@
       </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>MANUAL.pdf</t>
+          <t>E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="K298" s="4" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Mapa Pobreza XII Censo</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -17280,22 +17280,22 @@
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr">
         <is>
-          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>MANUAL.pdf</t>
         </is>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
         </is>
       </c>
       <c r="K299" s="4" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Mapa Pobreza XII Censo</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -17342,17 +17342,17 @@
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2025.pdf</t>
+          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
@@ -17399,17 +17399,17 @@
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2026.pdf</t>
+          <t>Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17456,17 +17456,17 @@
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2025.pdf</t>
+          <t>Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -17513,17 +17513,17 @@
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2026-1.pdf</t>
+          <t>Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -17565,22 +17565,22 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MIRANDA.pdf</t>
+          <t>Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -17632,12 +17632,12 @@
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MONAGAS.pdf</t>
+          <t>ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -17689,12 +17689,12 @@
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MERIDA.pdf</t>
+          <t>ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -17741,17 +17741,17 @@
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-1.pdf</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -17793,22 +17793,22 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-1.pdf</t>
+          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Noticias-Septiembre-1-1.pdf</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>Notas_Nov_2025.pdf</t>
+          <t>Noticias-Septiembre-1-1.pdf</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-1-1.pdf</t>
         </is>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -17907,22 +17907,22 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -17964,22 +17964,22 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>Resumen_OCTUBRE_2025.pdf</t>
+          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="K311" s="4" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18021,22 +18021,22 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18078,22 +18078,22 @@
       </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -18145,12 +18145,12 @@
       </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -18192,22 +18192,22 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K315" s="4" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -18254,17 +18254,17 @@
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K316" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Programación</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18311,17 +18311,17 @@
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Registros Administrativos Economicos</t>
+          <t>Programación</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18363,22 +18363,22 @@
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Revista ÁGORA</t>
+          <t>Registros Administrativos Economicos</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18420,22 +18420,22 @@
       </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>REVISTA-AGORA-1.pdf</t>
+          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Revista ÁGORA</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18482,17 +18482,17 @@
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18534,22 +18534,22 @@
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -18596,17 +18596,17 @@
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -18648,22 +18648,22 @@
       </c>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K323" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -18705,22 +18705,22 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K324" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -18762,22 +18762,22 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>Tipologia.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -18824,17 +18824,17 @@
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Tipologia.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -18876,22 +18876,22 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-TACHIRA.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -18933,22 +18933,22 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>ART2GOBDELFUTURO.pdf</t>
+          <t>ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -18990,22 +18990,22 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-YARACUY.pdf</t>
+          <t>ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -19057,12 +19057,12 @@
       </c>
       <c r="I330" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ZULIA.pdf</t>
+          <t>ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="K330" s="4" t="inlineStr">
@@ -19084,7 +19084,7 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -19104,22 +19104,22 @@
       </c>
       <c r="G331" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I331" s="4" t="inlineStr">
         <is>
-          <t>vision-metodologica.pdf</t>
+          <t>ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="K331" s="4" t="inlineStr">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E332" s="4" t="inlineStr">
@@ -19161,22 +19161,22 @@
       </c>
       <c r="G332" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I332" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ARAGUA.pdf</t>
+          <t>vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="K332" s="4" t="inlineStr">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Censo de zonas afectadas del estado Vargas</t>
+          <t>Aragua</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -19218,22 +19218,22 @@
       </c>
       <c r="G333" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I333" s="4" t="inlineStr">
         <is>
-          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="J333" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="K333" s="4" t="inlineStr">
@@ -19255,7 +19255,7 @@
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares 1967-1997</t>
+          <t>Censo de zonas afectadas del estado Vargas</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -19280,17 +19280,17 @@
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I334" s="4" t="inlineStr">
         <is>
-          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="J334" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="K334" s="4" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>Encuesta Hogares 1967-1997</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -19332,22 +19332,22 @@
       </c>
       <c r="G335" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I335" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua_compressed.pdf</t>
+          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="J335" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="K335" s="4" t="inlineStr">
@@ -19369,7 +19369,7 @@
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Estado Aragua</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="G336" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -19399,12 +19399,12 @@
       </c>
       <c r="I336" s="4" t="inlineStr">
         <is>
-          <t>VIVIENDA.pdf</t>
+          <t>Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="J336" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="K336" s="4" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Vivienda</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -19436,12 +19436,12 @@
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G337" s="4" t="inlineStr">
@@ -19451,17 +19451,17 @@
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I337" s="4" t="inlineStr">
         <is>
-          <t>Aragua.xls</t>
+          <t>VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="J337" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="K337" s="4" t="inlineStr">
@@ -19513,12 +19513,12 @@
       </c>
       <c r="I338" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-1.xls</t>
+          <t>Aragua.xls</t>
         </is>
       </c>
       <c r="J338" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
         </is>
       </c>
       <c r="K338" s="4" t="inlineStr">
@@ -19570,12 +19570,12 @@
       </c>
       <c r="I339" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua.xls</t>
+          <t>Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="J339" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="K339" s="4" t="inlineStr">
@@ -19627,15 +19627,72 @@
       </c>
       <c r="I340" s="4" t="inlineStr">
         <is>
+          <t>Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J340" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K340" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E341" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H341" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I341" s="4" t="inlineStr">
+        <is>
           <t>Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="J340" s="4" t="inlineStr">
+      <c r="J341" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="K340" s="4" t="inlineStr">
+      <c r="K341" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/</t>
         </is>
@@ -19721,7 +19778,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -19768,7 +19825,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14">
@@ -19778,7 +19835,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -19798,7 +19855,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17">
@@ -19808,7 +19865,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>2980320</v>
+        <v>2962561</v>
       </c>
     </row>
     <row r="18">

--- a/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
+++ b/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K341"/>
+  <dimension ref="A1:K347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12958,12 +12958,12 @@
       </c>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t>Coeficiente-GINI-2025-1.xlsx</t>
+          <t>COEFICIENTE-GINI.xlsx</t>
         </is>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Coeficiente-GINI-2025-1.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/COEFICIENTE-GINI.xlsx</t>
         </is>
       </c>
       <c r="K223" s="4" t="inlineStr">
@@ -13015,12 +13015,12 @@
       </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
-          <t>TRABAJO-1999-2025-1.xlsx</t>
+          <t>TRABAJO.xlsx</t>
         </is>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/TRABAJO-1999-2025-1.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/TRABAJO.xlsx</t>
         </is>
       </c>
       <c r="K224" s="4" t="inlineStr">
@@ -13099,22 +13099,22 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Población 1950-2050</t>
+          <t>Por Entidad y Sexo</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Población</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -13124,17 +13124,17 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
-          <t>1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
+          <t>Entidad-Federal-y-Sexo.xls</t>
         </is>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Entidad-Federal-y-Sexo.xls</t>
         </is>
       </c>
       <c r="K226" s="4" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Edad Simple</t>
+          <t>Población 1950-2050</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -13181,17 +13181,17 @@
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t>EDAD-SIMPLE.xls</t>
+          <t>1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
         </is>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
         </is>
       </c>
       <c r="K227" s="4" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Esperanza de Vida</t>
+          <t>Edad Simple</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
-          <t>ESPERANZA-DE-VIDA.xls</t>
+          <t>EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="K228" s="4" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Esperanza de Vida</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -13300,12 +13300,12 @@
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>Nacional-36.xls</t>
+          <t>ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="K229" s="4" t="inlineStr">
@@ -13327,42 +13327,42 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>7T FILVEN</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
+          <t>Nacional-36.xls</t>
         </is>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
         </is>
       </c>
       <c r="K230" s="4" t="inlineStr">
@@ -13384,22 +13384,22 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Por Parroquias</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -13409,17 +13409,17 @@
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ABRIL_2025.pdf</t>
+          <t>PROYECCION-POBLACION-PARROQUIAS.xls</t>
         </is>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ABRIL_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/PROYECCION-POBLACION-PARROQUIAS.xls</t>
         </is>
       </c>
       <c r="K231" s="4" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>7T FILVEN</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -13461,22 +13461,22 @@
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ABRIL_2026.pdf</t>
+          <t>TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
         </is>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/05/Resumen_ABRIL_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
         </is>
       </c>
       <c r="K232" s="4" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="I233" s="4" t="inlineStr">
         <is>
-          <t>Resumen_AGOSTO_2025.pdf</t>
+          <t>Resumen_ABRIL_2025.pdf</t>
         </is>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_AGOSTO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ABRIL_2025.pdf</t>
         </is>
       </c>
       <c r="K233" s="4" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -13580,17 +13580,17 @@
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="I234" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto-9.pdf</t>
+          <t>Resumen_ABRIL_2026.pdf</t>
         </is>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-9.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/05/Resumen_ABRIL_2026.pdf</t>
         </is>
       </c>
       <c r="K234" s="4" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -13632,22 +13632,22 @@
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I235" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-AMAZONAS.pdf</t>
+          <t>Resumen_AGOSTO_2025.pdf</t>
         </is>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-AMAZONAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_AGOSTO_2025.pdf</t>
         </is>
       </c>
       <c r="K235" s="4" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -13689,22 +13689,22 @@
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ANZOATEGUI.pdf</t>
+          <t>Noticias-Agosto-9.pdf</t>
         </is>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ANZOATEGUI.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-9.pdf</t>
         </is>
       </c>
       <c r="K236" s="4" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="I237" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-APURE.pdf</t>
+          <t>ESTADO-AMAZONAS.pdf</t>
         </is>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-APURE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-AMAZONAS.pdf</t>
         </is>
       </c>
       <c r="K237" s="4" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Aviso Oficial Fe de Vida 2026</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -13803,22 +13803,22 @@
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
+          <t>ESTADO-ANZOATEGUI.pdf</t>
         </is>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/01/AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ANZOATEGUI.pdf</t>
         </is>
       </c>
       <c r="K238" s="4" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="I239" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-BARINAS.pdf</t>
+          <t>ESTADO-APURE.pdf</t>
         </is>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BARINAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-APURE.pdf</t>
         </is>
       </c>
       <c r="K239" s="4" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Aviso Oficial Fe de Vida 2026</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -13917,22 +13917,22 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="I240" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-BOLIVAR.pdf</t>
+          <t>AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BOLIVAR.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/01/AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="K240" s="4" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>CATÁLOGO ACADÉMICO</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -13979,17 +13979,17 @@
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I241" s="4" t="inlineStr">
         <is>
-          <t>CatalogoDic2025-modificado.pdf</t>
+          <t>ESTADO-BARINAS.pdf</t>
         </is>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/12/CatalogoDic2025-modificado.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BARINAS.pdf</t>
         </is>
       </c>
       <c r="K241" s="4" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -14031,22 +14031,22 @@
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I242" s="4" t="inlineStr">
         <is>
-          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>ESTADO-BOLIVAR.pdf</t>
         </is>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BOLIVAR.pdf</t>
         </is>
       </c>
       <c r="K242" s="4" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>CATÁLOGO ACADÉMICO</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -14093,17 +14093,17 @@
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="I243" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-CARABOBO.pdf</t>
+          <t>CatalogoDic2025-modificado.pdf</t>
         </is>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-CARABOBO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/12/CatalogoDic2025-modificado.pdf</t>
         </is>
       </c>
       <c r="K243" s="4" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -14145,22 +14145,22 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I244" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-COJEDES.pdf</t>
+          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-COJEDES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="K244" s="4" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Defensa Integral de la Nación e Innovación en la Fuerza Armada Nacional Bolivariana</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -14202,22 +14202,22 @@
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I245" s="4" t="inlineStr">
         <is>
-          <t>ART1DEFENSAINTEGRAL.pdf</t>
+          <t>ESTADO-CARABOBO.pdf</t>
         </is>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART1DEFENSAINTEGRAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-CARABOBO.pdf</t>
         </is>
       </c>
       <c r="K245" s="4" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -14269,12 +14269,12 @@
       </c>
       <c r="I246" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-DELTA-AMACURO.pdf</t>
+          <t>ESTADO-COJEDES.pdf</t>
         </is>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-DELTA-AMACURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-COJEDES.pdf</t>
         </is>
       </c>
       <c r="K246" s="4" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Dependencias Federales</t>
+          <t>Defensa Integral de la Nación e Innovación en la Fuerza Armada Nacional Bolivariana</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -14316,22 +14316,22 @@
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I247" s="4" t="inlineStr">
         <is>
-          <t>Folleto-de-las-Dependencias-Federales.pdf</t>
+          <t>ART1DEFENSAINTEGRAL.pdf</t>
         </is>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-de-las-Dependencias-Federales.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART1DEFENSAINTEGRAL.pdf</t>
         </is>
       </c>
       <c r="K247" s="4" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Diciembre</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -14373,22 +14373,22 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
+          <t>ESTADO-DELTA-AMACURO.pdf</t>
         </is>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-DELTA-AMACURO.pdf</t>
         </is>
       </c>
       <c r="K248" s="4" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Directrices</t>
+          <t>Dependencias Federales</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -14430,22 +14430,22 @@
       </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I249" s="4" t="inlineStr">
         <is>
-          <t>DIRECTRICES.pdf</t>
+          <t>Folleto-de-las-Dependencias-Federales.pdf</t>
         </is>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/DIRECTRICES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-de-las-Dependencias-Federales.pdf</t>
         </is>
       </c>
       <c r="K249" s="4" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -14487,22 +14487,22 @@
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
+          <t>RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K250" s="4" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Directrices</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -14544,22 +14544,22 @@
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr">
         <is>
-          <t>DISTRITO-CAPITAL.pdf</t>
+          <t>DIRECTRICES.pdf</t>
         </is>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/DISTRITO-CAPITAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/DIRECTRICES.pdf</t>
         </is>
       </c>
       <c r="K251" s="4" t="inlineStr">
@@ -14581,19 +14581,19 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
+          <t>Distrito Capital</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>Publicaciones</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
           <t>Documento</t>
         </is>
       </c>
-      <c r="D252" s="4" t="inlineStr">
-        <is>
-          <t>Publicaciones</t>
-        </is>
-      </c>
-      <c r="E252" s="4" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
@@ -14611,12 +14611,12 @@
       </c>
       <c r="I252" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTO-SEGEN.pdf</t>
+          <t>Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
         </is>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/DOCUMENTO-SEGEN.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
         </is>
       </c>
       <c r="K252" s="4" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Documento Técnico EHM</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -14658,22 +14658,22 @@
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTO-TECNICO-EHM.pdf</t>
+          <t>DISTRITO-CAPITAL.pdf</t>
         </is>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/DOCUMENTO-TECNICO-EHM.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/DISTRITO-CAPITAL.pdf</t>
         </is>
       </c>
       <c r="K253" s="4" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>El Estado Docente y sus implicaciones jurídicas-filosóficas</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -14715,22 +14715,22 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr">
         <is>
-          <t>ART5ESTADODOCENTE.pdf</t>
+          <t>DOCUMENTO-SEGEN.pdf</t>
         </is>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART5ESTADODOCENTE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/DOCUMENTO-SEGEN.pdf</t>
         </is>
       </c>
       <c r="K254" s="4" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Documento Técnico EHM</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -14772,22 +14772,22 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN_NOTAS_ENERO_2026.pdf</t>
+          <t>DOCUMENTO-TECNICO-EHM.pdf</t>
         </is>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_ENERO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/DOCUMENTO-TECNICO-EHM.pdf</t>
         </is>
       </c>
       <c r="K255" s="4" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>El Estado Docente y sus implicaciones jurídicas-filosóficas</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -14834,17 +14834,17 @@
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I256" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ENERO_2025.pdf</t>
+          <t>ART5ESTADODOCENTE.pdf</t>
         </is>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ENERO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART5ESTADODOCENTE.pdf</t>
         </is>
       </c>
       <c r="K256" s="4" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Estado Amazonas</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -14886,22 +14886,22 @@
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I257" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
+          <t>RESUMEN_NOTAS_ENERO_2026.pdf</t>
         </is>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_ENERO_2026.pdf</t>
         </is>
       </c>
       <c r="K257" s="4" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Estado Anzoátegui</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -14943,22 +14943,22 @@
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I258" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
+          <t>Resumen_ENERO_2025.pdf</t>
         </is>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ENERO_2025.pdf</t>
         </is>
       </c>
       <c r="K258" s="4" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Estado Apure</t>
+          <t>Estado Amazonas</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -15010,12 +15010,12 @@
       </c>
       <c r="I259" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Apure-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Apure-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K259" s="4" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Estado Barinas</t>
+          <t>Estado Anzoátegui</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -15067,12 +15067,12 @@
       </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
+          <t>Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K260" s="4" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Estado Bolívar</t>
+          <t>Estado Apure</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -15124,12 +15124,12 @@
       </c>
       <c r="I261" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Apure-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Apure-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K261" s="4" t="inlineStr">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Estado Carabobo</t>
+          <t>Estado Barinas</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -15181,12 +15181,12 @@
       </c>
       <c r="I262" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
+          <t>Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
         </is>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
         </is>
       </c>
       <c r="K262" s="4" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Estado Cojedes</t>
+          <t>Estado Bolívar</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -15238,12 +15238,12 @@
       </c>
       <c r="I263" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes.pdf</t>
+          <t>Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Cojedes.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K263" s="4" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Estado Delta Amacuro</t>
+          <t>Estado Carabobo</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="I264" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K264" s="4" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Estado Falcón</t>
+          <t>Estado Cojedes</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="I265" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Falcon-INE-2025.pdf</t>
+          <t>Estado-Cojedes.pdf</t>
         </is>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Falcon-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Cojedes.pdf</t>
         </is>
       </c>
       <c r="K265" s="4" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Estado Guárico</t>
+          <t>Estado Delta Amacuro</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="I266" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico_20250620_153508_0000.pdf</t>
+          <t>Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Guarico_20250620_153508_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K266" s="4" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Estado La Guaira</t>
+          <t>Estado Falcón</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="I267" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira.pdf</t>
+          <t>Folleto-del-Estado-Falcon-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-La-Guaira.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Falcon-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K267" s="4" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Estado Lara</t>
+          <t>Estado Guárico</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="I268" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Lara-INE-2025.pdf</t>
+          <t>Estado-Guarico_20250620_153508_0000.pdf</t>
         </is>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Lara-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Guarico_20250620_153508_0000.pdf</t>
         </is>
       </c>
       <c r="K268" s="4" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Estado Miranda</t>
+          <t>Estado La Guaira</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -15580,12 +15580,12 @@
       </c>
       <c r="I269" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Miranda-INE-2025.pdf</t>
+          <t>Estado-La-Guaira.pdf</t>
         </is>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Miranda-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-La-Guaira.pdf</t>
         </is>
       </c>
       <c r="K269" s="4" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Estado Monagas</t>
+          <t>Estado Lara</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -15637,12 +15637,12 @@
       </c>
       <c r="I270" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Monagas-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Lara-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Monagas-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Lara-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K270" s="4" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Estado Mérida</t>
+          <t>Estado Miranda</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -15694,12 +15694,12 @@
       </c>
       <c r="I271" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Merida-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Miranda-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Merida-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Miranda-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Estado Nueva Esparta</t>
+          <t>Estado Monagas</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -15751,12 +15751,12 @@
       </c>
       <c r="I272" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
+          <t>Folleto-del-Estado-Monagas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Monagas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K272" s="4" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Estado Portuguesa</t>
+          <t>Estado Mérida</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="I273" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
+          <t>Folleto-del-Estado-Merida-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Merida-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K273" s="4" t="inlineStr">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Estado Sucre</t>
+          <t>Estado Nueva Esparta</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="I274" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Sucre-INE-2025.pdf</t>
+          <t>Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
         </is>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Sucre-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
         </is>
       </c>
       <c r="K274" s="4" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Estado Trujillo</t>
+          <t>Estado Portuguesa</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -15912,22 +15912,22 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I275" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Folleto-Portuguesa-_20260922_184008_0000.pdf</t>
         </is>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Folleto-Portuguesa-_20260922_184008_0000.pdf</t>
         </is>
       </c>
       <c r="K275" s="4" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Estado Táchira</t>
+          <t>Estado Sucre</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="I276" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Estado-Tachira.pdf</t>
+          <t>Folleto-del-Estado-Sucre-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Tachira.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Sucre-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K276" s="4" t="inlineStr">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Estado Yaracuy</t>
+          <t>Estado Trujillo</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="I277" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy_20250619_231832_0000.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Yaracuy_20250619_231832_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K277" s="4" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Estado Zulia</t>
+          <t>Estado Táchira</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -16093,12 +16093,12 @@
       </c>
       <c r="I278" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Zulia-INE-2025.pdf</t>
+          <t>Folleto-Estado-Tachira.pdf</t>
         </is>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Zulia-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Tachira.pdf</t>
         </is>
       </c>
       <c r="K278" s="4" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas Basadas en Registros</t>
+          <t>Estado Yaracuy</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -16140,22 +16140,22 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I279" s="4" t="inlineStr">
         <is>
-          <t>ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
+          <t>Estado-Yaracuy_20250619_231832_0000.pdf</t>
         </is>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Yaracuy_20250619_231832_0000.pdf</t>
         </is>
       </c>
       <c r="K279" s="4" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Estudio de la narrativa audiovisual como espacio de autodescubrimiento</t>
+          <t>Estado Zulia</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -16197,22 +16197,22 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I280" s="4" t="inlineStr">
         <is>
-          <t>ART6CINEYSUBJETIVIDAD.pdf</t>
+          <t>Folleto-del-Estado-Zulia-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART6CINEYSUBJETIVIDAD.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Zulia-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K280" s="4" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Estadísticas Basadas en Registros</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -16254,22 +16254,22 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I281" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-FALCON.pdf</t>
+          <t>ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-FALCON.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K281" s="4" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Estudio de la narrativa audiovisual como espacio de autodescubrimiento</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -16316,17 +16316,17 @@
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I282" s="4" t="inlineStr">
         <is>
-          <t>Resumen_FEBRERO_2025.pdf</t>
+          <t>ART6CINEYSUBJETIVIDAD.pdf</t>
         </is>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_FEBRERO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART6CINEYSUBJETIVIDAD.pdf</t>
         </is>
       </c>
       <c r="K282" s="4" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -16368,22 +16368,22 @@
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I283" s="4" t="inlineStr">
         <is>
-          <t>febrero.pdf</t>
+          <t>ESTADO-FALCON.pdf</t>
         </is>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/febrero.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-FALCON.pdf</t>
         </is>
       </c>
       <c r="K283" s="4" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Flyer</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -16425,22 +16425,22 @@
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I284" s="4" t="inlineStr">
         <is>
-          <t>Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
+          <t>Resumen_FEBRERO_2025.pdf</t>
         </is>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_FEBRERO_2025.pdf</t>
         </is>
       </c>
       <c r="K284" s="4" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Folleto en PDF</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -16482,22 +16482,22 @@
       </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I285" s="4" t="inlineStr">
         <is>
-          <t>TRANSICION-DEMOGRAFICA.pdf</t>
+          <t>febrero.pdf</t>
         </is>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/TRANSICION-DEMOGRAFICA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/febrero.pdf</t>
         </is>
       </c>
       <c r="K285" s="4" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Formato de Fe de Vida 2026</t>
+          <t>Flyer</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -16539,22 +16539,22 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I286" s="4" t="inlineStr">
         <is>
-          <t>FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
+          <t>Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
         </is>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/01/FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
         </is>
       </c>
       <c r="K286" s="4" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Gestion y Mantenimiento</t>
+          <t>Folleto en PDF</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -16601,17 +16601,17 @@
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I287" s="4" t="inlineStr">
         <is>
-          <t>GESTION-Y-MANTENIMIENTO.pdf</t>
+          <t>TRANSICION-DEMOGRAFICA.pdf</t>
         </is>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/GESTION-Y-MANTENIMIENTO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/TRANSICION-DEMOGRAFICA.pdf</t>
         </is>
       </c>
       <c r="K287" s="4" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Grandes Misiones Habitacionales</t>
+          <t>Formato de Fe de Vida 2026</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -16658,17 +16658,17 @@
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
-          <t>Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
+          <t>FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/01/FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="K288" s="4" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>Gestion y Mantenimiento</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-GUARICO.pdf</t>
+          <t>GESTION-Y-MANTENIMIENTO.pdf</t>
         </is>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-GUARICO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/GESTION-Y-MANTENIMIENTO.pdf</t>
         </is>
       </c>
       <c r="K289" s="4" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>INE – FILVEN</t>
+          <t>Grandes Misiones Habitacionales</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -16767,22 +16767,22 @@
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
+          <t>Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
         </is>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
         </is>
       </c>
       <c r="K290" s="4" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -16824,22 +16824,22 @@
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr">
         <is>
-          <t>25-anos-Encuesta-Industrial-.pdf</t>
+          <t>ESTADO-GUARICO.pdf</t>
         </is>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/25-anos-Encuesta-Industrial-.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-GUARICO.pdf</t>
         </is>
       </c>
       <c r="K291" s="4" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>INE – FILVEN</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -16881,22 +16881,22 @@
       </c>
       <c r="G292" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JULIO_2025.pdf</t>
+          <t>TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
         </is>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JULIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
         </is>
       </c>
       <c r="K292" s="4" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -16943,17 +16943,17 @@
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I293" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Julio-31.pdf</t>
+          <t>25-anos-Encuesta-Industrial-.pdf</t>
         </is>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/25-anos-Encuesta-Industrial-.pdf</t>
         </is>
       </c>
       <c r="K293" s="4" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -17005,12 +17005,12 @@
       </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JUNIO_2025.pdf</t>
+          <t>Resumen_JULIO_2025.pdf</t>
         </is>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JULIO_2025.pdf</t>
         </is>
       </c>
       <c r="K294" s="4" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr">
         <is>
-          <t>Noticias-12-06-al-19-06.pdf</t>
+          <t>Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="K295" s="4" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -17109,22 +17109,22 @@
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LA-GUAIRA.pdf</t>
+          <t>Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="K296" s="4" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -17166,22 +17166,22 @@
       </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I297" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LARA.pdf</t>
+          <t>Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="K297" s="4" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Las escala subregional y local en la planificación</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -17223,22 +17223,22 @@
       </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="K298" s="4" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -17280,22 +17280,22 @@
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr">
         <is>
-          <t>MANUAL.pdf</t>
+          <t>ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="K299" s="4" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Mapa Pobreza XII Censo</t>
+          <t>Las escala subregional y local en la planificación</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -17342,17 +17342,17 @@
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -17394,22 +17394,22 @@
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2025.pdf</t>
+          <t>MANUAL.pdf</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
         </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Mapa Pobreza XII Censo</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17461,12 +17461,12 @@
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2026.pdf</t>
+          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -17518,12 +17518,12 @@
       </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2025.pdf</t>
+          <t>Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -17570,17 +17570,17 @@
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2026-1.pdf</t>
+          <t>Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -17622,22 +17622,22 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MIRANDA.pdf</t>
+          <t>Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -17679,22 +17679,22 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MONAGAS.pdf</t>
+          <t>Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Metadatos de Personas</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -17736,22 +17736,22 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MERIDA.pdf</t>
+          <t>METADATOS-DE-PERSONAS.pdf</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/METADATOS-DE-PERSONAS.pdf</t>
         </is>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -17798,17 +17798,17 @@
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-1-1.pdf</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -17850,22 +17850,22 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-1-1.pdf</t>
+          <t>ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-1-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -17907,22 +17907,22 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>Notas_Nov_2025.pdf</t>
+          <t>ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -17969,17 +17969,17 @@
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="K311" s="4" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Noticias-Septiembre-3-1.pdf</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18026,17 +18026,17 @@
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>Resumen_OCTUBRE_2025.pdf</t>
+          <t>Noticias-Septiembre-3-1.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-3-1.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18078,22 +18078,22 @@
       </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -18135,22 +18135,22 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -18192,22 +18192,22 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K315" s="4" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -18254,17 +18254,17 @@
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K316" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Programación</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18363,22 +18363,22 @@
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Registros Administrativos Economicos</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18420,22 +18420,22 @@
       </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Revista ÁGORA</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18477,22 +18477,22 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>REVISTA-AGORA-1.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Programación</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18534,22 +18534,22 @@
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Registros Administrativos Economicos</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -18601,12 +18601,12 @@
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Revista ÁGORA</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -18648,22 +18648,22 @@
       </c>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="K323" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -18705,22 +18705,22 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K324" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -18762,22 +18762,22 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>Noticias-Septiembre-4-1.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-4-1.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -18819,22 +18819,22 @@
       </c>
       <c r="G326" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>Tipologia.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -18876,22 +18876,22 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -18943,12 +18943,12 @@
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-TACHIRA.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -18990,22 +18990,22 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>ART2GOBDELFUTURO.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -19047,22 +19047,22 @@
       </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I330" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-YARACUY.pdf</t>
+          <t>Tipologia.pdf</t>
         </is>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
         </is>
       </c>
       <c r="K330" s="4" t="inlineStr">
@@ -19084,7 +19084,7 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -19104,22 +19104,22 @@
       </c>
       <c r="G331" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I331" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ZULIA.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K331" s="4" t="inlineStr">
@@ -19141,7 +19141,7 @@
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -19161,22 +19161,22 @@
       </c>
       <c r="G332" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I332" s="4" t="inlineStr">
         <is>
-          <t>vision-metodologica.pdf</t>
+          <t>ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="K332" s="4" t="inlineStr">
@@ -19198,12 +19198,12 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -19218,22 +19218,22 @@
       </c>
       <c r="G333" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I333" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ARAGUA.pdf</t>
+          <t>ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="J333" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="K333" s="4" t="inlineStr">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Censo de zonas afectadas del estado Vargas</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E334" s="4" t="inlineStr">
@@ -19275,22 +19275,22 @@
       </c>
       <c r="G334" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I334" s="4" t="inlineStr">
         <is>
-          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="J334" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="K334" s="4" t="inlineStr">
@@ -19312,12 +19312,12 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares 1967-1997</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
@@ -19332,22 +19332,22 @@
       </c>
       <c r="G335" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I335" s="4" t="inlineStr">
         <is>
-          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="J335" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="K335" s="4" t="inlineStr">
@@ -19369,12 +19369,12 @@
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E336" s="4" t="inlineStr">
@@ -19389,22 +19389,22 @@
       </c>
       <c r="G336" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I336" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua_compressed.pdf</t>
+          <t>vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="J336" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="K336" s="4" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Aragua</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -19446,22 +19446,22 @@
       </c>
       <c r="G337" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I337" s="4" t="inlineStr">
         <is>
-          <t>VIVIENDA.pdf</t>
+          <t>ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="J337" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="K337" s="4" t="inlineStr">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Censo de zonas afectadas del estado Vargas</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -19493,12 +19493,12 @@
       </c>
       <c r="E338" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
@@ -19508,17 +19508,17 @@
       </c>
       <c r="H338" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I338" s="4" t="inlineStr">
         <is>
-          <t>Aragua.xls</t>
+          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="J338" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="K338" s="4" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Encuesta Hogares 1967-1997</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -19550,12 +19550,12 @@
       </c>
       <c r="E339" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -19565,17 +19565,17 @@
       </c>
       <c r="H339" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I339" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-1.xls</t>
+          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="J339" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="K339" s="4" t="inlineStr">
@@ -19597,7 +19597,7 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Estado Aragua</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -19607,32 +19607,32 @@
       </c>
       <c r="E340" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G340" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I340" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua.xls</t>
+          <t>Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="J340" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="K340" s="4" t="inlineStr">
@@ -19654,45 +19654,387 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
+          <t>Metadatos de Hogares</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E341" s="4" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H341" s="4" t="inlineStr">
+        <is>
+          <t>septiembre</t>
+        </is>
+      </c>
+      <c r="I341" s="4" t="inlineStr">
+        <is>
+          <t>METADATOS-DE-HOGARES.pdf</t>
+        </is>
+      </c>
+      <c r="J341" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/METADATOS-DE-HOGARES.pdf</t>
+        </is>
+      </c>
+      <c r="K341" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>Metadatos de Viviendas</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E342" s="4" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="F342" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H342" s="4" t="inlineStr">
+        <is>
+          <t>septiembre</t>
+        </is>
+      </c>
+      <c r="I342" s="4" t="inlineStr">
+        <is>
+          <t>ETADATOS-DE-VIVIENDAS.pdf</t>
+        </is>
+      </c>
+      <c r="J342" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ETADATOS-DE-VIVIENDAS.pdf</t>
+        </is>
+      </c>
+      <c r="K342" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B343" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda</t>
+        </is>
+      </c>
+      <c r="D343" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E343" s="4" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="F343" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="G343" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H343" s="4" t="inlineStr">
+        <is>
+          <t>julio</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr">
+        <is>
+          <t>VIVIENDA.pdf</t>
+        </is>
+      </c>
+      <c r="J343" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+        </is>
+      </c>
+      <c r="K343" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
           <t>Aragua</t>
         </is>
       </c>
-      <c r="D341" s="4" t="inlineStr">
+      <c r="D344" s="4" t="inlineStr">
         <is>
           <t>Vivienda y servicios</t>
         </is>
       </c>
-      <c r="E341" s="4" t="inlineStr">
-        <is>
-          <t>Dato tabular</t>
-        </is>
-      </c>
-      <c r="F341" s="4" t="inlineStr">
+      <c r="E344" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F344" s="4" t="inlineStr">
         <is>
           <t>XLS</t>
         </is>
       </c>
-      <c r="G341" s="4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H341" s="4" t="inlineStr">
-        <is>
-          <t>abril</t>
-        </is>
-      </c>
-      <c r="I341" s="4" t="inlineStr">
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H344" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I344" s="4" t="inlineStr">
+        <is>
+          <t>Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J344" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K344" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D345" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E345" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G345" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H345" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I345" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua-1.xls</t>
+        </is>
+      </c>
+      <c r="J345" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+        </is>
+      </c>
+      <c r="K345" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D346" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E346" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F346" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G346" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H346" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I346" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J346" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K346" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D347" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E347" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F347" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G347" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H347" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I347" s="4" t="inlineStr">
         <is>
           <t>Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="J341" s="4" t="inlineStr">
+      <c r="J347" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="K341" s="4" t="inlineStr">
+      <c r="K347" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/</t>
         </is>
@@ -19778,7 +20120,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -19825,7 +20167,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14">
@@ -19835,7 +20177,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -19845,7 +20187,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
@@ -19855,7 +20197,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17">
@@ -19865,7 +20207,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>2962561</v>
+        <v>2983947</v>
       </c>
     </row>
     <row r="18">

--- a/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
+++ b/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-3-1.pdf</t>
+          <t>Noticias-Septiembre-3-2.pdf</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18031,12 +18031,12 @@
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-3-1.pdf</t>
+          <t>Noticias-Septiembre-3-2.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-3-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-3-2.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -18762,22 +18762,22 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-4-1.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-4-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -18824,17 +18824,17 @@
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -18876,22 +18876,22 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -18933,22 +18933,22 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Tabulados PDF</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -18990,22 +18990,22 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>UNIFICADO.pdf</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/UNIFICADO.pdf</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares 1967-1997</t>
+          <t>Encuesta Hogares por Muestreo</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
+++ b/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K347"/>
+  <dimension ref="A1:K350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Por Entidad y Sexo</t>
+          <t>Estructura de la Población</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -13109,12 +13109,12 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -13124,17 +13124,17 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
-          <t>Entidad-Federal-y-Sexo.xls</t>
+          <t>ESTRUCTURA-DE-LA-POBLACION-1.pdf</t>
         </is>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Entidad-Federal-y-Sexo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/ESTRUCTURA-DE-LA-POBLACION-1.pdf</t>
         </is>
       </c>
       <c r="K226" s="4" t="inlineStr">
@@ -13156,22 +13156,22 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Población 1950-2050</t>
+          <t>Por Entidad y Sexo</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Población</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -13181,17 +13181,17 @@
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t>1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
+          <t>Entidad-Federal-y-Sexo.xls</t>
         </is>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Entidad-Federal-y-Sexo.xls</t>
         </is>
       </c>
       <c r="K227" s="4" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Edad Simple</t>
+          <t>Población 1950-2050</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -13238,17 +13238,17 @@
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
-          <t>EDAD-SIMPLE.xls</t>
+          <t>1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
         </is>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
         </is>
       </c>
       <c r="K228" s="4" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Esperanza de Vida</t>
+          <t>Edad Simple</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -13300,12 +13300,12 @@
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>ESPERANZA-DE-VIDA.xls</t>
+          <t>EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="K229" s="4" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Esperanza de Vida</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
-          <t>Nacional-36.xls</t>
+          <t>ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="K230" s="4" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Por Parroquias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -13409,17 +13409,17 @@
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>PROYECCION-POBLACION-PARROQUIAS.xls</t>
+          <t>Nacional-36.xls</t>
         </is>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/PROYECCION-POBLACION-PARROQUIAS.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
         </is>
       </c>
       <c r="K231" s="4" t="inlineStr">
@@ -13441,42 +13441,42 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>7T FILVEN</t>
+          <t>Por Parroquias</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
+          <t>PROYECCION-POBLACION-PARROQUIAS.xls</t>
         </is>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/PROYECCION-POBLACION-PARROQUIAS.xls</t>
         </is>
       </c>
       <c r="K232" s="4" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>7T FILVEN</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -13518,22 +13518,22 @@
       </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I233" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ABRIL_2025.pdf</t>
+          <t>TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
         </is>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ABRIL_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
         </is>
       </c>
       <c r="K233" s="4" t="inlineStr">
@@ -13580,17 +13580,17 @@
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I234" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ABRIL_2026.pdf</t>
+          <t>Resumen_ABRIL_2025.pdf</t>
         </is>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/05/Resumen_ABRIL_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ABRIL_2025.pdf</t>
         </is>
       </c>
       <c r="K234" s="4" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -13637,17 +13637,17 @@
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="I235" s="4" t="inlineStr">
         <is>
-          <t>Resumen_AGOSTO_2025.pdf</t>
+          <t>Resumen_ABRIL_2026.pdf</t>
         </is>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_AGOSTO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/05/Resumen_ABRIL_2026.pdf</t>
         </is>
       </c>
       <c r="K235" s="4" t="inlineStr">
@@ -13694,17 +13694,17 @@
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto-9.pdf</t>
+          <t>Resumen_AGOSTO_2025.pdf</t>
         </is>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-9.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_AGOSTO_2025.pdf</t>
         </is>
       </c>
       <c r="K236" s="4" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -13746,22 +13746,22 @@
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I237" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-AMAZONAS.pdf</t>
+          <t>Noticias-Agosto-9.pdf</t>
         </is>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-AMAZONAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-9.pdf</t>
         </is>
       </c>
       <c r="K237" s="4" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -13813,12 +13813,12 @@
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ANZOATEGUI.pdf</t>
+          <t>ESTADO-AMAZONAS.pdf</t>
         </is>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ANZOATEGUI.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-AMAZONAS.pdf</t>
         </is>
       </c>
       <c r="K238" s="4" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="I239" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-APURE.pdf</t>
+          <t>ESTADO-ANZOATEGUI.pdf</t>
         </is>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-APURE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ANZOATEGUI.pdf</t>
         </is>
       </c>
       <c r="K239" s="4" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Aviso Oficial Fe de Vida 2026</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -13917,22 +13917,22 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I240" s="4" t="inlineStr">
         <is>
-          <t>AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
+          <t>ESTADO-APURE.pdf</t>
         </is>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/01/AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-APURE.pdf</t>
         </is>
       </c>
       <c r="K240" s="4" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Aviso Oficial Fe de Vida 2026</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -13974,22 +13974,22 @@
       </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="I241" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-BARINAS.pdf</t>
+          <t>AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BARINAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/01/AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="K241" s="4" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -14041,12 +14041,12 @@
       </c>
       <c r="I242" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-BOLIVAR.pdf</t>
+          <t>ESTADO-BARINAS.pdf</t>
         </is>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BOLIVAR.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BARINAS.pdf</t>
         </is>
       </c>
       <c r="K242" s="4" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>CATÁLOGO ACADÉMICO</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -14093,17 +14093,17 @@
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I243" s="4" t="inlineStr">
         <is>
-          <t>CatalogoDic2025-modificado.pdf</t>
+          <t>ESTADO-BOLIVAR.pdf</t>
         </is>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/12/CatalogoDic2025-modificado.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BOLIVAR.pdf</t>
         </is>
       </c>
       <c r="K243" s="4" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>CATÁLOGO ACADÉMICO</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -14145,22 +14145,22 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="I244" s="4" t="inlineStr">
         <is>
-          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>CatalogoDic2025-modificado.pdf</t>
         </is>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/12/CatalogoDic2025-modificado.pdf</t>
         </is>
       </c>
       <c r="K244" s="4" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -14202,22 +14202,22 @@
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I245" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-CARABOBO.pdf</t>
+          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-CARABOBO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="K245" s="4" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -14269,12 +14269,12 @@
       </c>
       <c r="I246" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-COJEDES.pdf</t>
+          <t>ESTADO-CARABOBO.pdf</t>
         </is>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-COJEDES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-CARABOBO.pdf</t>
         </is>
       </c>
       <c r="K246" s="4" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Defensa Integral de la Nación e Innovación en la Fuerza Armada Nacional Bolivariana</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -14316,22 +14316,22 @@
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I247" s="4" t="inlineStr">
         <is>
-          <t>ART1DEFENSAINTEGRAL.pdf</t>
+          <t>ESTADO-COJEDES.pdf</t>
         </is>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART1DEFENSAINTEGRAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-COJEDES.pdf</t>
         </is>
       </c>
       <c r="K247" s="4" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Defensa Integral de la Nación e Innovación en la Fuerza Armada Nacional Bolivariana</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -14373,22 +14373,22 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-DELTA-AMACURO.pdf</t>
+          <t>ART1DEFENSAINTEGRAL.pdf</t>
         </is>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-DELTA-AMACURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART1DEFENSAINTEGRAL.pdf</t>
         </is>
       </c>
       <c r="K248" s="4" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Dependencias Federales</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -14435,17 +14435,17 @@
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I249" s="4" t="inlineStr">
         <is>
-          <t>Folleto-de-las-Dependencias-Federales.pdf</t>
+          <t>ESTADO-DELTA-AMACURO.pdf</t>
         </is>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-de-las-Dependencias-Federales.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-DELTA-AMACURO.pdf</t>
         </is>
       </c>
       <c r="K249" s="4" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Diciembre</t>
+          <t>Dependencias Federales</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -14487,22 +14487,22 @@
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
+          <t>Folleto-de-las-Dependencias-Federales.pdf</t>
         </is>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-de-las-Dependencias-Federales.pdf</t>
         </is>
       </c>
       <c r="K250" s="4" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Directrices</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -14544,22 +14544,22 @@
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr">
         <is>
-          <t>DIRECTRICES.pdf</t>
+          <t>RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/DIRECTRICES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K251" s="4" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Directrices</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -14601,22 +14601,22 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I252" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
+          <t>DIRECTRICES.pdf</t>
         </is>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/DIRECTRICES.pdf</t>
         </is>
       </c>
       <c r="K252" s="4" t="inlineStr">
@@ -14663,17 +14663,17 @@
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr">
         <is>
-          <t>DISTRITO-CAPITAL.pdf</t>
+          <t>Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
         </is>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/DISTRITO-CAPITAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
         </is>
       </c>
       <c r="K253" s="4" t="inlineStr">
@@ -14695,19 +14695,19 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
+          <t>Distrito Capital</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
+        <is>
+          <t>Publicaciones</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
           <t>Documento</t>
         </is>
       </c>
-      <c r="D254" s="4" t="inlineStr">
-        <is>
-          <t>Publicaciones</t>
-        </is>
-      </c>
-      <c r="E254" s="4" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
@@ -14720,17 +14720,17 @@
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTO-SEGEN.pdf</t>
+          <t>DISTRITO-CAPITAL.pdf</t>
         </is>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/DOCUMENTO-SEGEN.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/DISTRITO-CAPITAL.pdf</t>
         </is>
       </c>
       <c r="K254" s="4" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Documento Técnico EHM</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -14772,22 +14772,22 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTO-TECNICO-EHM.pdf</t>
+          <t>DOCUMENTO-SEGEN.pdf</t>
         </is>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/DOCUMENTO-TECNICO-EHM.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/DOCUMENTO-SEGEN.pdf</t>
         </is>
       </c>
       <c r="K255" s="4" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>El Estado Docente y sus implicaciones jurídicas-filosóficas</t>
+          <t>Documento Técnico EHM</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -14829,22 +14829,22 @@
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I256" s="4" t="inlineStr">
         <is>
-          <t>ART5ESTADODOCENTE.pdf</t>
+          <t>DOCUMENTO-TECNICO-EHM.pdf</t>
         </is>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART5ESTADODOCENTE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/DOCUMENTO-TECNICO-EHM.pdf</t>
         </is>
       </c>
       <c r="K256" s="4" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>El Estado Docente y sus implicaciones jurídicas-filosóficas</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I257" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN_NOTAS_ENERO_2026.pdf</t>
+          <t>ART5ESTADODOCENTE.pdf</t>
         </is>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_ENERO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART5ESTADODOCENTE.pdf</t>
         </is>
       </c>
       <c r="K257" s="4" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="I258" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ENERO_2025.pdf</t>
+          <t>RESUMEN_NOTAS_ENERO_2026.pdf</t>
         </is>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ENERO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_ENERO_2026.pdf</t>
         </is>
       </c>
       <c r="K258" s="4" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Estado Amazonas</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -15000,22 +15000,22 @@
       </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I259" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
+          <t>Resumen_ENERO_2025.pdf</t>
         </is>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ENERO_2025.pdf</t>
         </is>
       </c>
       <c r="K259" s="4" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Estado Anzoátegui</t>
+          <t>Estado Amazonas</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -15067,12 +15067,12 @@
       </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K260" s="4" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Estado Apure</t>
+          <t>Estado Anzoátegui</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -15124,12 +15124,12 @@
       </c>
       <c r="I261" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Apure-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Apure-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K261" s="4" t="inlineStr">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Estado Barinas</t>
+          <t>Estado Apure</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -15181,12 +15181,12 @@
       </c>
       <c r="I262" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
+          <t>Folleto-del-Estado-Apure-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Apure-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K262" s="4" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Estado Bolívar</t>
+          <t>Estado Barinas</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -15238,12 +15238,12 @@
       </c>
       <c r="I263" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
+          <t>Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
         </is>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
         </is>
       </c>
       <c r="K263" s="4" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Estado Carabobo</t>
+          <t>Estado Bolívar</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="I264" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K264" s="4" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Estado Cojedes</t>
+          <t>Estado Carabobo</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="I265" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes.pdf</t>
+          <t>Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Cojedes.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K265" s="4" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Estado Delta Amacuro</t>
+          <t>Estado Cojedes</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="I266" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
+          <t>Estado-Cojedes.pdf</t>
         </is>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Cojedes.pdf</t>
         </is>
       </c>
       <c r="K266" s="4" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Estado Falcón</t>
+          <t>Estado Delta Amacuro</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="I267" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Falcon-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Falcon-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K267" s="4" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Estado Guárico</t>
+          <t>Estado Falcón</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="I268" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico_20250620_153508_0000.pdf</t>
+          <t>Folleto-del-Estado-Falcon-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Guarico_20250620_153508_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Falcon-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K268" s="4" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Estado La Guaira</t>
+          <t>Estado Guárico</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -15580,12 +15580,12 @@
       </c>
       <c r="I269" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira.pdf</t>
+          <t>Estado-Guarico_20250620_153508_0000.pdf</t>
         </is>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-La-Guaira.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Guarico_20250620_153508_0000.pdf</t>
         </is>
       </c>
       <c r="K269" s="4" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Estado Lara</t>
+          <t>Estado La Guaira</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -15637,12 +15637,12 @@
       </c>
       <c r="I270" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Lara-INE-2025.pdf</t>
+          <t>Estado-La-Guaira.pdf</t>
         </is>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Lara-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-La-Guaira.pdf</t>
         </is>
       </c>
       <c r="K270" s="4" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Estado Miranda</t>
+          <t>Estado Lara</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -15694,12 +15694,12 @@
       </c>
       <c r="I271" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Miranda-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Lara-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Miranda-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Lara-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Estado Monagas</t>
+          <t>Estado Miranda</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -15751,12 +15751,12 @@
       </c>
       <c r="I272" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Monagas-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Miranda-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Monagas-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Miranda-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K272" s="4" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Estado Mérida</t>
+          <t>Estado Monagas</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="I273" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Merida-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Monagas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Merida-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Monagas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K273" s="4" t="inlineStr">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Estado Nueva Esparta</t>
+          <t>Estado Mérida</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="I274" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
+          <t>Folleto-del-Estado-Merida-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Merida-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K274" s="4" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Estado Portuguesa</t>
+          <t>Estado Nueva Esparta</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -15912,22 +15912,22 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I275" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Portuguesa-_20260922_184008_0000.pdf</t>
+          <t>Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
         </is>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Folleto-Portuguesa-_20260922_184008_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
         </is>
       </c>
       <c r="K275" s="4" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Estado Sucre</t>
+          <t>Estado Portuguesa</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -15969,22 +15969,22 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I276" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Sucre-INE-2025.pdf</t>
+          <t>Folleto-Portuguesa-_20260922_184008_0000.pdf</t>
         </is>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Sucre-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Folleto-Portuguesa-_20260922_184008_0000.pdf</t>
         </is>
       </c>
       <c r="K276" s="4" t="inlineStr">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Estado Trujillo</t>
+          <t>Estado Sucre</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="I277" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Folleto-del-Estado-Sucre-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Sucre-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K277" s="4" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Estado Táchira</t>
+          <t>Estado Trujillo</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -16093,12 +16093,12 @@
       </c>
       <c r="I278" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Estado-Tachira.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Tachira.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K278" s="4" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Estado Yaracuy</t>
+          <t>Estado Táchira</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -16150,12 +16150,12 @@
       </c>
       <c r="I279" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy_20250619_231832_0000.pdf</t>
+          <t>Folleto-Estado-Tachira.pdf</t>
         </is>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Yaracuy_20250619_231832_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Tachira.pdf</t>
         </is>
       </c>
       <c r="K279" s="4" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Estado Zulia</t>
+          <t>Estado Yaracuy</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -16207,12 +16207,12 @@
       </c>
       <c r="I280" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Zulia-INE-2025.pdf</t>
+          <t>Estado-Yaracuy_20250619_231832_0000.pdf</t>
         </is>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Zulia-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Yaracuy_20250619_231832_0000.pdf</t>
         </is>
       </c>
       <c r="K280" s="4" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas Basadas en Registros</t>
+          <t>Estado Zulia</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -16254,22 +16254,22 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I281" s="4" t="inlineStr">
         <is>
-          <t>ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
+          <t>Folleto-del-Estado-Zulia-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Zulia-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K281" s="4" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Estudio de la narrativa audiovisual como espacio de autodescubrimiento</t>
+          <t>Estadísticas Basadas en Registros</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -16311,22 +16311,22 @@
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I282" s="4" t="inlineStr">
         <is>
-          <t>ART6CINEYSUBJETIVIDAD.pdf</t>
+          <t>ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART6CINEYSUBJETIVIDAD.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K282" s="4" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Estudio de la narrativa audiovisual como espacio de autodescubrimiento</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -16368,22 +16368,22 @@
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I283" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-FALCON.pdf</t>
+          <t>ART6CINEYSUBJETIVIDAD.pdf</t>
         </is>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-FALCON.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART6CINEYSUBJETIVIDAD.pdf</t>
         </is>
       </c>
       <c r="K283" s="4" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -16425,22 +16425,22 @@
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I284" s="4" t="inlineStr">
         <is>
-          <t>Resumen_FEBRERO_2025.pdf</t>
+          <t>ESTADO-FALCON.pdf</t>
         </is>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_FEBRERO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-FALCON.pdf</t>
         </is>
       </c>
       <c r="K284" s="4" t="inlineStr">
@@ -16487,17 +16487,17 @@
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I285" s="4" t="inlineStr">
         <is>
-          <t>febrero.pdf</t>
+          <t>Resumen_FEBRERO_2025.pdf</t>
         </is>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/febrero.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_FEBRERO_2025.pdf</t>
         </is>
       </c>
       <c r="K285" s="4" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Flyer</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -16539,22 +16539,22 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I286" s="4" t="inlineStr">
         <is>
-          <t>Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
+          <t>febrero.pdf</t>
         </is>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/febrero.pdf</t>
         </is>
       </c>
       <c r="K286" s="4" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Folleto en PDF</t>
+          <t>Flyer</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -16601,17 +16601,17 @@
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I287" s="4" t="inlineStr">
         <is>
-          <t>TRANSICION-DEMOGRAFICA.pdf</t>
+          <t>Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
         </is>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/TRANSICION-DEMOGRAFICA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
         </is>
       </c>
       <c r="K287" s="4" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Formato de Fe de Vida 2026</t>
+          <t>Folleto en PDF</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -16653,22 +16653,22 @@
       </c>
       <c r="G288" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
-          <t>FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
+          <t>TRANSICION-DEMOGRAFICA.pdf</t>
         </is>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/01/FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/TRANSICION-DEMOGRAFICA.pdf</t>
         </is>
       </c>
       <c r="K288" s="4" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Gestion y Mantenimiento</t>
+          <t>Formato de Fe de Vida 2026</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr">
         <is>
-          <t>GESTION-Y-MANTENIMIENTO.pdf</t>
+          <t>FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/GESTION-Y-MANTENIMIENTO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/01/FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="K289" s="4" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Grandes Misiones Habitacionales</t>
+          <t>Gestion y Mantenimiento</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -16767,22 +16767,22 @@
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
-          <t>Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
+          <t>GESTION-Y-MANTENIMIENTO.pdf</t>
         </is>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/GESTION-Y-MANTENIMIENTO.pdf</t>
         </is>
       </c>
       <c r="K290" s="4" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>Grandes Misiones Habitacionales</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -16824,22 +16824,22 @@
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-GUARICO.pdf</t>
+          <t>Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
         </is>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-GUARICO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
         </is>
       </c>
       <c r="K291" s="4" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>INE – FILVEN</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -16886,17 +16886,17 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
+          <t>ESTADO-GUARICO.pdf</t>
         </is>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-GUARICO.pdf</t>
         </is>
       </c>
       <c r="K292" s="4" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>INE – FILVEN</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -16938,22 +16938,22 @@
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I293" s="4" t="inlineStr">
         <is>
-          <t>25-anos-Encuesta-Industrial-.pdf</t>
+          <t>TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
         </is>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/25-anos-Encuesta-Industrial-.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
         </is>
       </c>
       <c r="K293" s="4" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JULIO_2025.pdf</t>
+          <t>25-anos-Encuesta-Industrial-.pdf</t>
         </is>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JULIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/25-anos-Encuesta-Industrial-.pdf</t>
         </is>
       </c>
       <c r="K294" s="4" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Julio-31.pdf</t>
+          <t>Resumen_JULIO_2025.pdf</t>
         </is>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JULIO_2025.pdf</t>
         </is>
       </c>
       <c r="K295" s="4" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -17114,17 +17114,17 @@
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JUNIO_2025.pdf</t>
+          <t>Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="K296" s="4" t="inlineStr">
@@ -17171,17 +17171,17 @@
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I297" s="4" t="inlineStr">
         <is>
-          <t>Noticias-12-06-al-19-06.pdf</t>
+          <t>Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="K297" s="4" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -17223,22 +17223,22 @@
       </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LA-GUAIRA.pdf</t>
+          <t>Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="K298" s="4" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -17290,12 +17290,12 @@
       </c>
       <c r="I299" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LARA.pdf</t>
+          <t>ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="K299" s="4" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Las escala subregional y local en la planificación</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -17337,22 +17337,22 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Las escala subregional y local en la planificación</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -17394,22 +17394,22 @@
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>MANUAL.pdf</t>
+          <t>E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Mapa Pobreza XII Censo</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17451,22 +17451,22 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>MANUAL.pdf</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Mapa Pobreza XII Censo</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -17513,17 +17513,17 @@
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2025.pdf</t>
+          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -17570,17 +17570,17 @@
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2026.pdf</t>
+          <t>Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -17627,17 +17627,17 @@
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2025.pdf</t>
+          <t>Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -17684,17 +17684,17 @@
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2026-1.pdf</t>
+          <t>Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Metadatos de Personas</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -17741,17 +17741,17 @@
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>METADATOS-DE-PERSONAS.pdf</t>
+          <t>Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/METADATOS-DE-PERSONAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Metadatos de Personas</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -17793,22 +17793,22 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MIRANDA.pdf</t>
+          <t>METADATOS-DE-PERSONAS.pdf</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/METADATOS-DE-PERSONAS.pdf</t>
         </is>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -17860,12 +17860,12 @@
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MONAGAS.pdf</t>
+          <t>ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -17917,12 +17917,12 @@
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MERIDA.pdf</t>
+          <t>ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -17969,17 +17969,17 @@
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="K311" s="4" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-3-2.pdf</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18021,22 +18021,22 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Septiembre-3-2.pdf</t>
+          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-3-2.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Noticias-octubre-3.pdf</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18083,17 +18083,17 @@
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>Notas_Nov_2025.pdf</t>
+          <t>Noticias-octubre-3.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-3.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -18135,22 +18135,22 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -18192,22 +18192,22 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>Resumen_OCTUBRE_2025.pdf</t>
+          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="K315" s="4" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -18249,22 +18249,22 @@
       </c>
       <c r="G316" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K316" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>Noticias-octubre-2.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-2.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18363,22 +18363,22 @@
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18420,22 +18420,22 @@
       </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18477,22 +18477,22 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Programación</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18544,12 +18544,12 @@
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Registros Administrativos Economicos</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -18591,22 +18591,22 @@
       </c>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Revista ÁGORA</t>
+          <t>Programación</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -18648,22 +18648,22 @@
       </c>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>REVISTA-AGORA-1.pdf</t>
+          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="K323" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Registros Administrativos Economicos</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -18705,22 +18705,22 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
         <is>
-          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="K324" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Revista ÁGORA</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -18762,22 +18762,22 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -18819,22 +18819,22 @@
       </c>
       <c r="G326" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -18876,22 +18876,22 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>Noticias-Septiembre-3-2.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-3-2.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -18938,17 +18938,17 @@
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Tabulados PDF</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -18990,22 +18990,22 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>UNIFICADO.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/UNIFICADO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -19047,22 +19047,22 @@
       </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I330" s="4" t="inlineStr">
         <is>
-          <t>Tipologia.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K330" s="4" t="inlineStr">
@@ -19084,7 +19084,7 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -19104,22 +19104,22 @@
       </c>
       <c r="G331" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I331" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K331" s="4" t="inlineStr">
@@ -19141,7 +19141,7 @@
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Tabulados PDF</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -19161,22 +19161,22 @@
       </c>
       <c r="G332" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I332" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-TACHIRA.pdf</t>
+          <t>UNIFICADO.pdf</t>
         </is>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/UNIFICADO.pdf</t>
         </is>
       </c>
       <c r="K332" s="4" t="inlineStr">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
+          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -19228,12 +19228,12 @@
       </c>
       <c r="I333" s="4" t="inlineStr">
         <is>
-          <t>ART2GOBDELFUTURO.pdf</t>
+          <t>Tipologia.pdf</t>
         </is>
       </c>
       <c r="J333" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
         </is>
       </c>
       <c r="K333" s="4" t="inlineStr">
@@ -19255,7 +19255,7 @@
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -19275,22 +19275,22 @@
       </c>
       <c r="G334" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I334" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-YARACUY.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J334" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K334" s="4" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -19342,12 +19342,12 @@
       </c>
       <c r="I335" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ZULIA.pdf</t>
+          <t>ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="J335" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="K335" s="4" t="inlineStr">
@@ -19369,7 +19369,7 @@
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
+          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -19399,12 +19399,12 @@
       </c>
       <c r="I336" s="4" t="inlineStr">
         <is>
-          <t>vision-metodologica.pdf</t>
+          <t>ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="J336" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="K336" s="4" t="inlineStr">
@@ -19426,12 +19426,12 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr">
@@ -19456,12 +19456,12 @@
       </c>
       <c r="I337" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ARAGUA.pdf</t>
+          <t>ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="J337" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="K337" s="4" t="inlineStr">
@@ -19483,12 +19483,12 @@
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>Censo de zonas afectadas del estado Vargas</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E338" s="4" t="inlineStr">
@@ -19503,22 +19503,22 @@
       </c>
       <c r="G338" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I338" s="4" t="inlineStr">
         <is>
-          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="J338" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="K338" s="4" t="inlineStr">
@@ -19540,12 +19540,12 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares por Muestreo</t>
+          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr">
@@ -19565,17 +19565,17 @@
       </c>
       <c r="H339" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I339" s="4" t="inlineStr">
         <is>
-          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="J339" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="K339" s="4" t="inlineStr">
@@ -19597,7 +19597,7 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>Aragua</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -19622,17 +19622,17 @@
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I340" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua_compressed.pdf</t>
+          <t>ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="J340" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="K340" s="4" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Metadatos de Hogares</t>
+          <t>Censo de zonas afectadas del estado Vargas</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -19679,17 +19679,17 @@
       </c>
       <c r="H341" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I341" s="4" t="inlineStr">
         <is>
-          <t>METADATOS-DE-HOGARES.pdf</t>
+          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="J341" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/METADATOS-DE-HOGARES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="K341" s="4" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Metadatos de Viviendas</t>
+          <t>Encuesta Hogares por Muestreo</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -19736,17 +19736,17 @@
       </c>
       <c r="H342" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I342" s="4" t="inlineStr">
         <is>
-          <t>ETADATOS-DE-VIVIENDAS.pdf</t>
+          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="J342" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ETADATOS-DE-VIVIENDAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="K342" s="4" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Estado Aragua</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="G343" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr">
@@ -19798,12 +19798,12 @@
       </c>
       <c r="I343" s="4" t="inlineStr">
         <is>
-          <t>VIVIENDA.pdf</t>
+          <t>Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="J343" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="K343" s="4" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Metadatos de Hogares</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -19835,12 +19835,12 @@
       </c>
       <c r="E344" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G344" s="4" t="inlineStr">
@@ -19850,17 +19850,17 @@
       </c>
       <c r="H344" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I344" s="4" t="inlineStr">
         <is>
-          <t>Aragua.xls</t>
+          <t>METADATOS-DE-HOGARES.pdf</t>
         </is>
       </c>
       <c r="J344" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/METADATOS-DE-HOGARES.pdf</t>
         </is>
       </c>
       <c r="K344" s="4" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Metadatos de Viviendas</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -19892,12 +19892,12 @@
       </c>
       <c r="E345" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -19907,17 +19907,17 @@
       </c>
       <c r="H345" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I345" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-1.xls</t>
+          <t>ETADATOS-DE-VIVIENDAS.pdf</t>
         </is>
       </c>
       <c r="J345" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ETADATOS-DE-VIVIENDAS.pdf</t>
         </is>
       </c>
       <c r="K345" s="4" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Vivienda</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -19949,12 +19949,12 @@
       </c>
       <c r="E346" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G346" s="4" t="inlineStr">
@@ -19964,17 +19964,17 @@
       </c>
       <c r="H346" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I346" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua.xls</t>
+          <t>VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="J346" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="K346" s="4" t="inlineStr">
@@ -20026,15 +20026,186 @@
       </c>
       <c r="I347" s="4" t="inlineStr">
         <is>
+          <t>Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J347" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K347" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E348" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F348" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G348" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H348" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I348" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua-1.xls</t>
+        </is>
+      </c>
+      <c r="J348" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+        </is>
+      </c>
+      <c r="K348" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E349" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F349" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G349" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H349" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I349" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J349" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K349" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E350" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F350" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G350" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H350" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I350" s="4" t="inlineStr">
+        <is>
           <t>Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="J347" s="4" t="inlineStr">
+      <c r="J350" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="K347" s="4" t="inlineStr">
+      <c r="K350" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/</t>
         </is>
@@ -20120,7 +20291,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -20167,7 +20338,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14">
@@ -20187,7 +20358,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
+++ b/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-3.pdf</t>
+          <t>Noticias-octubre-3-1.pdf</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18088,12 +18088,12 @@
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-3.pdf</t>
+          <t>Noticias-octubre-3-1.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-3.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-3-1.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-2.pdf</t>
+          <t>Noticias-octubre-3-2.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-2.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-3-2.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
+++ b/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-3-1.pdf</t>
+          <t>Noticias-octubre-5.pdf</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18088,12 +18088,12 @@
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-3-1.pdf</t>
+          <t>Noticias-octubre-5.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-3-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-5.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-3-2.pdf</t>
+          <t>Noticias-octubre-2-2.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-3-2.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-2-2.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
+++ b/assets/data/ine/catalog/catalogo_dataset_web_ove_ine_venezuela.xlsx
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-5.pdf</t>
+          <t>Noticias-octubre-7.pdf</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18088,12 +18088,12 @@
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-5.pdf</t>
+          <t>Noticias-octubre-7.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-5.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-7.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>Noticias-octubre-2-2.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/10/Noticias-octubre-2-2.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18363,22 +18363,22 @@
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18430,12 +18430,12 @@
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18477,22 +18477,22 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18539,17 +18539,17 @@
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Presidente</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -18591,22 +18591,22 @@
       </c>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>HOJA-INE-CAMILO.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/10/HOJA-INE-CAMILO.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
